--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="345">
   <si>
     <t>key</t>
   </si>
@@ -980,6 +980,72 @@
   </si>
   <si>
     <t>theme.toggle.label</t>
+  </si>
+  <si>
+    <t>offline.title</t>
+  </si>
+  <si>
+    <t>You're offline</t>
+  </si>
+  <si>
+    <t>Нет подключения</t>
+  </si>
+  <si>
+    <t>offline.message</t>
+  </si>
+  <si>
+    <t>Check your internet connection and try again.</t>
+  </si>
+  <si>
+    <t>Проверьте подключение к интернету и попробуйте снова.</t>
+  </si>
+  <si>
+    <t>common.stepOf</t>
+  </si>
+  <si>
+    <t>Step {current} of {total}</t>
+  </si>
+  <si>
+    <t>Шаг {current} из {total}</t>
+  </si>
+  <si>
+    <t>settings.section.account</t>
+  </si>
+  <si>
+    <t>settings.section.preferences</t>
+  </si>
+  <si>
+    <t>Preferences</t>
+  </si>
+  <si>
+    <t>Предпочтения</t>
+  </si>
+  <si>
+    <t>settings.section.support</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Поддержка</t>
+  </si>
+  <si>
+    <t>settings.section.session</t>
+  </si>
+  <si>
+    <t>Session</t>
+  </si>
+  <si>
+    <t>Сеанс</t>
+  </si>
+  <si>
+    <t>common.close</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Закрыть</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2650,8 +2716,96 @@
         <v>309</v>
       </c>
     </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>323</v>
+      </c>
+      <c r="B118" t="s">
+        <v>324</v>
+      </c>
+      <c r="C118" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>326</v>
+      </c>
+      <c r="B119" t="s">
+        <v>327</v>
+      </c>
+      <c r="C119" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>329</v>
+      </c>
+      <c r="B120" t="s">
+        <v>330</v>
+      </c>
+      <c r="C120" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>332</v>
+      </c>
+      <c r="B121" t="s">
+        <v>281</v>
+      </c>
+      <c r="C121" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>333</v>
+      </c>
+      <c r="B122" t="s">
+        <v>334</v>
+      </c>
+      <c r="C122" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>336</v>
+      </c>
+      <c r="B123" t="s">
+        <v>337</v>
+      </c>
+      <c r="C123" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>339</v>
+      </c>
+      <c r="B124" t="s">
+        <v>340</v>
+      </c>
+      <c r="C124" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>342</v>
+      </c>
+      <c r="B125" t="s">
+        <v>343</v>
+      </c>
+      <c r="C125" t="s">
+        <v>344</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="763">
   <si>
     <t>key</t>
   </si>
@@ -1046,6 +1046,1260 @@
   </si>
   <si>
     <t>Закрыть</t>
+  </si>
+  <si>
+    <t>app.update.title</t>
+  </si>
+  <si>
+    <t>Update available</t>
+  </si>
+  <si>
+    <t>Доступно обновление</t>
+  </si>
+  <si>
+    <t>app.update.message</t>
+  </si>
+  <si>
+    <t>Please update to the latest version of LawBid to keep using the app.</t>
+  </si>
+  <si>
+    <t>Пожалуйста, обновите приложение до последней версии, чтобы продолжить пользоваться LawBid.</t>
+  </si>
+  <si>
+    <t>app.update.button</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>Обновить</t>
+  </si>
+  <si>
+    <t>common.done</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Готово</t>
+  </si>
+  <si>
+    <t>common.optional</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>Необязательно</t>
+  </si>
+  <si>
+    <t>common.search</t>
+  </si>
+  <si>
+    <t>splash.loading</t>
+  </si>
+  <si>
+    <t>Loading LawBid…</t>
+  </si>
+  <si>
+    <t>Загружаем LawBid…</t>
+  </si>
+  <si>
+    <t>auth.phone.countryCode</t>
+  </si>
+  <si>
+    <t>US +1</t>
+  </si>
+  <si>
+    <t>auth.phone.hint</t>
+  </si>
+  <si>
+    <t>(555) 123-4567</t>
+  </si>
+  <si>
+    <t>auth.phone.useEmail</t>
+  </si>
+  <si>
+    <t>Use email instead</t>
+  </si>
+  <si>
+    <t>Войти по email</t>
+  </si>
+  <si>
+    <t>auth.email.title</t>
+  </si>
+  <si>
+    <t>Your email</t>
+  </si>
+  <si>
+    <t>Ваш email</t>
+  </si>
+  <si>
+    <t>auth.email.subtitle</t>
+  </si>
+  <si>
+    <t>We'll email you a 6-digit code. No password needed.</t>
+  </si>
+  <si>
+    <t>Мы отправим 6-значный код на почту. Пароль не нужен.</t>
+  </si>
+  <si>
+    <t>auth.email.hint</t>
+  </si>
+  <si>
+    <t>name@example.com</t>
+  </si>
+  <si>
+    <t>auth.email.fieldLabel</t>
+  </si>
+  <si>
+    <t>Email address</t>
+  </si>
+  <si>
+    <t>Адрес электронной почты</t>
+  </si>
+  <si>
+    <t>auth.email.error.invalid</t>
+  </si>
+  <si>
+    <t>Enter a valid email address</t>
+  </si>
+  <si>
+    <t>Введите корректный email</t>
+  </si>
+  <si>
+    <t>auth.email.usePhone</t>
+  </si>
+  <si>
+    <t>Use phone number instead</t>
+  </si>
+  <si>
+    <t>Войти по номеру телефона</t>
+  </si>
+  <si>
+    <t>error.api.NETWORK_ERROR</t>
+  </si>
+  <si>
+    <t>No connection. Check your internet and try again.</t>
+  </si>
+  <si>
+    <t>Нет соединения. Проверьте интернет и попробуйте снова.</t>
+  </si>
+  <si>
+    <t>error.api.VALIDATION_ERROR</t>
+  </si>
+  <si>
+    <t>Please check the entered data.</t>
+  </si>
+  <si>
+    <t>Проверьте введённые данные.</t>
+  </si>
+  <si>
+    <t>error.api.RATE_LIMITED</t>
+  </si>
+  <si>
+    <t>Too many attempts. Please try again later.</t>
+  </si>
+  <si>
+    <t>Слишком много попыток. Попробуйте позже.</t>
+  </si>
+  <si>
+    <t>error.api.retryAfter</t>
+  </si>
+  <si>
+    <t>Too many attempts. Try again in {seconds} s.</t>
+  </si>
+  <si>
+    <t>Слишком много попыток. Повторите через {seconds} с.</t>
+  </si>
+  <si>
+    <t>error.api.AUTH_OTP_INVALID</t>
+  </si>
+  <si>
+    <t>Incorrect code</t>
+  </si>
+  <si>
+    <t>Неверный код</t>
+  </si>
+  <si>
+    <t>error.api.AUTH_OTP_EXPIRED</t>
+  </si>
+  <si>
+    <t>The code has expired. Request a new one.</t>
+  </si>
+  <si>
+    <t>Код истёк, запросите новый</t>
+  </si>
+  <si>
+    <t>error.api.AUTH_OTP_LOCKED</t>
+  </si>
+  <si>
+    <t>Too many incorrect codes. Try again in 15 minutes.</t>
+  </si>
+  <si>
+    <t>Слишком много неверных кодов. Попробуйте через 15 минут.</t>
+  </si>
+  <si>
+    <t>error.api.AUTH_OTP_REQUEST_LIMIT</t>
+  </si>
+  <si>
+    <t>Too many code requests. Please try again later.</t>
+  </si>
+  <si>
+    <t>Слишком много запросов кода. Попробуйте позже.</t>
+  </si>
+  <si>
+    <t>error.api.CONTACT_DOMAIN_BLOCKED</t>
+  </si>
+  <si>
+    <t>This email can't be used. Please enter your real, personal email — private relay and temporary addresses aren't accepted.</t>
+  </si>
+  <si>
+    <t>Этот email нельзя использовать. Укажите вашу настоящую почту — скрытые (relay) и временные адреса не принимаются.</t>
+  </si>
+  <si>
+    <t>error.api.CONTACT_ALREADY_EXISTS</t>
+  </si>
+  <si>
+    <t>This contact is already linked to another LawBid account.</t>
+  </si>
+  <si>
+    <t>Этот контакт уже привязан к другому аккаунту LawBid.</t>
+  </si>
+  <si>
+    <t>error.api.PHONE_COUNTRY_NOT_SUPPORTED</t>
+  </si>
+  <si>
+    <t>Phone numbers from this country aren't supported yet. Please use a US number.</t>
+  </si>
+  <si>
+    <t>Номера этой страны пока не поддерживаются. Укажите номер США.</t>
+  </si>
+  <si>
+    <t>error.api.PROVIDER_BUDGET_EXCEEDED</t>
+  </si>
+  <si>
+    <t>We can't send codes right now. Please try again later.</t>
+  </si>
+  <si>
+    <t>Сейчас не получается отправить код. Попробуйте позже.</t>
+  </si>
+  <si>
+    <t>error.api.REAUTH_REQUIRED</t>
+  </si>
+  <si>
+    <t>Please confirm it's you first.</t>
+  </si>
+  <si>
+    <t>Сначала подтвердите, что это вы.</t>
+  </si>
+  <si>
+    <t>error.api.REAUTH_INVALID</t>
+  </si>
+  <si>
+    <t>Incorrect or expired confirmation code.</t>
+  </si>
+  <si>
+    <t>Неверный или просроченный код подтверждения.</t>
+  </si>
+  <si>
+    <t>error.api.NO_REAUTH_CONTACT</t>
+  </si>
+  <si>
+    <t>We couldn't confirm your identity: there is no verified contact on this account. Please contact support.</t>
+  </si>
+  <si>
+    <t>Не удалось подтвердить личность: в аккаунте нет подтверждённого контакта. Обратитесь в поддержку.</t>
+  </si>
+  <si>
+    <t>error.api.CLIENT_CONTACTS_INCOMPLETE</t>
+  </si>
+  <si>
+    <t>Verify both your phone and email to continue.</t>
+  </si>
+  <si>
+    <t>Чтобы продолжить, подтвердите и телефон, и email.</t>
+  </si>
+  <si>
+    <t>error.api.ONBOARDING_INCOMPLETE</t>
+  </si>
+  <si>
+    <t>A few required steps are still missing.</t>
+  </si>
+  <si>
+    <t>Остались незаполненные обязательные шаги.</t>
+  </si>
+  <si>
+    <t>error.api.ROLE_ALREADY_SET</t>
+  </si>
+  <si>
+    <t>Your role has already been chosen and can't be changed.</t>
+  </si>
+  <si>
+    <t>Роль уже выбрана, изменить её нельзя.</t>
+  </si>
+  <si>
+    <t>error.api.I18N_LANGUAGE_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>This language isn't available yet.</t>
+  </si>
+  <si>
+    <t>Этот язык пока недоступен.</t>
+  </si>
+  <si>
+    <t>error.api.ACCOUNT_SUSPENDED</t>
+  </si>
+  <si>
+    <t>error.api.ACCOUNT_DELETED</t>
+  </si>
+  <si>
+    <t>error.api.AUTH_PROVIDER_DISABLED</t>
+  </si>
+  <si>
+    <t>onboarding.continue</t>
+  </si>
+  <si>
+    <t>onboarding.language.title</t>
+  </si>
+  <si>
+    <t>Choose your language</t>
+  </si>
+  <si>
+    <t>Выберите язык</t>
+  </si>
+  <si>
+    <t>onboarding.language.subtitle</t>
+  </si>
+  <si>
+    <t>You can change it any time in Settings.</t>
+  </si>
+  <si>
+    <t>Его можно изменить в любой момент в настройках.</t>
+  </si>
+  <si>
+    <t>onboarding.consents.title</t>
+  </si>
+  <si>
+    <t>Before we start</t>
+  </si>
+  <si>
+    <t>Прежде чем начать</t>
+  </si>
+  <si>
+    <t>onboarding.consents.subtitle</t>
+  </si>
+  <si>
+    <t>LawBid is for adults only. Please review and accept the terms below.</t>
+  </si>
+  <si>
+    <t>LawBid только для совершеннолетних. Ознакомьтесь с условиями и примите их.</t>
+  </si>
+  <si>
+    <t>onboarding.consents.section.required</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Обязательно</t>
+  </si>
+  <si>
+    <t>onboarding.consents.section.optional</t>
+  </si>
+  <si>
+    <t>Optional — you can change these later</t>
+  </si>
+  <si>
+    <t>Необязательно — можно изменить позже</t>
+  </si>
+  <si>
+    <t>onboarding.consents.age18</t>
+  </si>
+  <si>
+    <t>I am 18 years of age or older</t>
+  </si>
+  <si>
+    <t>Мне 18 лет или больше</t>
+  </si>
+  <si>
+    <t>onboarding.consents.terms</t>
+  </si>
+  <si>
+    <t>I accept the Terms of Service and Privacy Policy</t>
+  </si>
+  <si>
+    <t>Я принимаю Условия использования и Политику конфиденциальности</t>
+  </si>
+  <si>
+    <t>onboarding.consents.disclaimer.title</t>
+  </si>
+  <si>
+    <t>LawBid is not a law firm</t>
+  </si>
+  <si>
+    <t>LawBid — не юридическая фирма</t>
+  </si>
+  <si>
+    <t>onboarding.consents.disclaimer.body</t>
+  </si>
+  <si>
+    <t>LawBid is not a law firm and does not provide legal services. Using the service does not create an attorney-client relationship.</t>
+  </si>
+  <si>
+    <t>LawBid не является юридической фирмой и не оказывает юридических услуг. Использование сервиса не создаёт отношений адвокат-клиент.</t>
+  </si>
+  <si>
+    <t>onboarding.consents.disclaimer.accept</t>
+  </si>
+  <si>
+    <t>I understand and agree</t>
+  </si>
+  <si>
+    <t>Я понимаю и согласен(на)</t>
+  </si>
+  <si>
+    <t>onboarding.consents.marketingEmail</t>
+  </si>
+  <si>
+    <t>Product news and offers by email</t>
+  </si>
+  <si>
+    <t>Новости и предложения по email</t>
+  </si>
+  <si>
+    <t>onboarding.consents.marketingPush</t>
+  </si>
+  <si>
+    <t>Product news and offers by push notification</t>
+  </si>
+  <si>
+    <t>Новости и предложения в push-уведомлениях</t>
+  </si>
+  <si>
+    <t>onboarding.consents.analytics</t>
+  </si>
+  <si>
+    <t>Help improve LawBid with anonymous usage analytics</t>
+  </si>
+  <si>
+    <t>Помогать улучшать LawBid анонимной аналитикой</t>
+  </si>
+  <si>
+    <t>onboarding.consents.requiredHint</t>
+  </si>
+  <si>
+    <t>Please accept the required items above to continue.</t>
+  </si>
+  <si>
+    <t>Чтобы продолжить, отметьте обязательные пункты выше.</t>
+  </si>
+  <si>
+    <t>legal.doc.terms</t>
+  </si>
+  <si>
+    <t>Terms of Service</t>
+  </si>
+  <si>
+    <t>legal.doc.privacy</t>
+  </si>
+  <si>
+    <t>Политика конфиденциальности</t>
+  </si>
+  <si>
+    <t>legal.doc.disclaimer</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>Дисклеймер</t>
+  </si>
+  <si>
+    <t>legal.doc.client_contact_sharing</t>
+  </si>
+  <si>
+    <t>Contact sharing consent</t>
+  </si>
+  <si>
+    <t>Согласие на передачу контактов</t>
+  </si>
+  <si>
+    <t>legal.doc.document</t>
+  </si>
+  <si>
+    <t>Legal document</t>
+  </si>
+  <si>
+    <t>Правовой документ</t>
+  </si>
+  <si>
+    <t>legal.version</t>
+  </si>
+  <si>
+    <t>Version {version}</t>
+  </si>
+  <si>
+    <t>Версия {version}</t>
+  </si>
+  <si>
+    <t>legal.unavailable</t>
+  </si>
+  <si>
+    <t>We couldn't load this document. Check your connection and try again.</t>
+  </si>
+  <si>
+    <t>Не удалось загрузить документ. Проверьте соединение и попробуйте снова.</t>
+  </si>
+  <si>
+    <t>legal.notFound</t>
+  </si>
+  <si>
+    <t>This document hasn't been published yet.</t>
+  </si>
+  <si>
+    <t>Этот документ ещё не опубликован.</t>
+  </si>
+  <si>
+    <t>legal.copyLink</t>
+  </si>
+  <si>
+    <t>Copy</t>
+  </si>
+  <si>
+    <t>Копировать</t>
+  </si>
+  <si>
+    <t>legal.linkCopied</t>
+  </si>
+  <si>
+    <t>Link copied</t>
+  </si>
+  <si>
+    <t>Ссылка скопирована</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.title</t>
+  </si>
+  <si>
+    <t>Verify your contacts</t>
+  </si>
+  <si>
+    <t>Подтвердите контакты</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.subtitle.client</t>
+  </si>
+  <si>
+    <t>To publish cases you need a verified phone AND email. Attorneys see them only after you accept their offer.</t>
+  </si>
+  <si>
+    <t>Для публикации кейсов нужны подтверждённые телефон И email. Адвокат увидит их только после того, как вы примете его предложение.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.subtitle.attorney</t>
+  </si>
+  <si>
+    <t>A verified phone is required. A work email is recommended for subscription receipts.</t>
+  </si>
+  <si>
+    <t>Нужен подтверждённый телефон. Рабочий email рекомендуется — на него придут чеки подписки.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.phone.title</t>
+  </si>
+  <si>
+    <t>Телефон</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.email.title</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.phone.why</t>
+  </si>
+  <si>
+    <t>We'll text you a 6-digit code.</t>
+  </si>
+  <si>
+    <t>Мы отправим SMS с 6-значным кодом.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.email.why</t>
+  </si>
+  <si>
+    <t>Use your real, personal email — relay and temporary addresses aren't accepted.</t>
+  </si>
+  <si>
+    <t>Укажите настоящую почту — скрытые (relay) и временные адреса не принимаются.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.status.verified</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Подтверждён</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.status.required</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.status.recommended</t>
+  </si>
+  <si>
+    <t>Recommended</t>
+  </si>
+  <si>
+    <t>Рекомендуется</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.sendCode</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.confirmIdentity</t>
+  </si>
+  <si>
+    <t>First, confirm it's you: enter the code we sent to {target}.</t>
+  </si>
+  <si>
+    <t>Сначала подтвердите, что это вы: введите код, отправленный на {target}.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.codeSent</t>
+  </si>
+  <si>
+    <t>Enter the code we sent to {target}.</t>
+  </si>
+  <si>
+    <t>Введите код, отправленный на {target}.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.change</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Изменить</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.missing.phone</t>
+  </si>
+  <si>
+    <t>Verify your phone to continue.</t>
+  </si>
+  <si>
+    <t>Чтобы продолжить, подтвердите телефон.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.missing.email</t>
+  </si>
+  <si>
+    <t>Verify your email to continue.</t>
+  </si>
+  <si>
+    <t>Чтобы продолжить, подтвердите email.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.missing.phone_email</t>
+  </si>
+  <si>
+    <t>Verify your phone and email to continue.</t>
+  </si>
+  <si>
+    <t>Чтобы продолжить, подтвердите телефон и email.</t>
+  </si>
+  <si>
+    <t>onboarding.contacts.privacy</t>
+  </si>
+  <si>
+    <t>Your contacts stay private: they're never shown publicly and are shared only with the attorney whose offer you accept.</t>
+  </si>
+  <si>
+    <t>Ваши контакты скрыты: они не показываются публично и передаются только адвокату, чьё предложение вы примете.</t>
+  </si>
+  <si>
+    <t>onboarding.profile.title.client</t>
+  </si>
+  <si>
+    <t>About you</t>
+  </si>
+  <si>
+    <t>О вас</t>
+  </si>
+  <si>
+    <t>onboarding.profile.title.attorney</t>
+  </si>
+  <si>
+    <t>Your attorney profile</t>
+  </si>
+  <si>
+    <t>Профиль адвоката</t>
+  </si>
+  <si>
+    <t>onboarding.profile.subtitle.client</t>
+  </si>
+  <si>
+    <t>This helps us match you with attorneys in your state who speak your language.</t>
+  </si>
+  <si>
+    <t>Так мы подберём адвокатов в вашем штате, говорящих на вашем языке.</t>
+  </si>
+  <si>
+    <t>onboarding.profile.subtitle.attorney</t>
+  </si>
+  <si>
+    <t>The basics clients see first. License details come with verification.</t>
+  </si>
+  <si>
+    <t>Основное, что увидят клиенты. Данные лицензии добавите при верификации.</t>
+  </si>
+  <si>
+    <t>onboarding.profile.firstName</t>
+  </si>
+  <si>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Имя</t>
+  </si>
+  <si>
+    <t>onboarding.profile.lastName</t>
+  </si>
+  <si>
+    <t>Last name</t>
+  </si>
+  <si>
+    <t>Фамилия</t>
+  </si>
+  <si>
+    <t>onboarding.profile.realNameHint</t>
+  </si>
+  <si>
+    <t>Use your real name — it's shown to attorneys only after you accept an offer.</t>
+  </si>
+  <si>
+    <t>Укажите настоящее имя — адвокат увидит его только после принятия предложения.</t>
+  </si>
+  <si>
+    <t>onboarding.profile.bio</t>
+  </si>
+  <si>
+    <t>Short bio</t>
+  </si>
+  <si>
+    <t>Коротко о себе</t>
+  </si>
+  <si>
+    <t>onboarding.profile.bioHint</t>
+  </si>
+  <si>
+    <t>Experience, focus areas, how you work with clients</t>
+  </si>
+  <si>
+    <t>Опыт, специализация, как вы работаете с клиентами</t>
+  </si>
+  <si>
+    <t>onboarding.profile.firm</t>
+  </si>
+  <si>
+    <t>Firm name</t>
+  </si>
+  <si>
+    <t>Название фирмы</t>
+  </si>
+  <si>
+    <t>onboarding.profile.state</t>
+  </si>
+  <si>
+    <t>State of residence</t>
+  </si>
+  <si>
+    <t>Штат проживания</t>
+  </si>
+  <si>
+    <t>onboarding.profile.licensedStates</t>
+  </si>
+  <si>
+    <t>States where you're licensed</t>
+  </si>
+  <si>
+    <t>Штаты, где у вас есть лицензия</t>
+  </si>
+  <si>
+    <t>onboarding.profile.languages</t>
+  </si>
+  <si>
+    <t>Languages you speak</t>
+  </si>
+  <si>
+    <t>Языки общения</t>
+  </si>
+  <si>
+    <t>onboarding.profile.select</t>
+  </si>
+  <si>
+    <t>Select</t>
+  </si>
+  <si>
+    <t>Выбрать</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactMethod</t>
+  </si>
+  <si>
+    <t>Preferred way to be contacted (optional)</t>
+  </si>
+  <si>
+    <t>Предпочтительный способ связи (необязательно)</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactMethod.call</t>
+  </si>
+  <si>
+    <t>Call</t>
+  </si>
+  <si>
+    <t>Звонок</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactMethod.sms</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactMethod.email</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactMethod.chat</t>
+  </si>
+  <si>
+    <t>In-app chat</t>
+  </si>
+  <si>
+    <t>Чат в приложении</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactTime</t>
+  </si>
+  <si>
+    <t>Convenient time (optional)</t>
+  </si>
+  <si>
+    <t>Удобное время (необязательно)</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactTimeHint</t>
+  </si>
+  <si>
+    <t>e.g. weekdays after 6 pm</t>
+  </si>
+  <si>
+    <t>например, будни после 18:00</t>
+  </si>
+  <si>
+    <t>onboarding.profile.contactHint</t>
+  </si>
+  <si>
+    <t>Shared with an attorney only after you accept their offer.</t>
+  </si>
+  <si>
+    <t>Передаётся адвокату только после принятия его предложения.</t>
+  </si>
+  <si>
+    <t>onboarding.profile.error.required</t>
+  </si>
+  <si>
+    <t>Обязательное поле</t>
+  </si>
+  <si>
+    <t>onboarding.push.title</t>
+  </si>
+  <si>
+    <t>Stay in the loop</t>
+  </si>
+  <si>
+    <t>Будьте в курсе</t>
+  </si>
+  <si>
+    <t>onboarding.push.subtitle</t>
+  </si>
+  <si>
+    <t>Notifications tell you the moment something needs your attention.</t>
+  </si>
+  <si>
+    <t>Уведомления сообщат, как только потребуется ваше внимание.</t>
+  </si>
+  <si>
+    <t>onboarding.push.benefit1.client</t>
+  </si>
+  <si>
+    <t>New offers from attorneys on your case</t>
+  </si>
+  <si>
+    <t>Новые предложения адвокатов по вашему кейсу</t>
+  </si>
+  <si>
+    <t>onboarding.push.benefit1.attorney</t>
+  </si>
+  <si>
+    <t>New cases in your practice areas and states</t>
+  </si>
+  <si>
+    <t>Новые кейсы по вашим практикам и штатам</t>
+  </si>
+  <si>
+    <t>onboarding.push.benefit2</t>
+  </si>
+  <si>
+    <t>New messages in your chats</t>
+  </si>
+  <si>
+    <t>Новые сообщения в чатах</t>
+  </si>
+  <si>
+    <t>onboarding.push.benefit3</t>
+  </si>
+  <si>
+    <t>Important account and case updates</t>
+  </si>
+  <si>
+    <t>Важные изменения по аккаунту и кейсам</t>
+  </si>
+  <si>
+    <t>onboarding.push.footnote</t>
+  </si>
+  <si>
+    <t>You can change this any time in Settings → Notifications.</t>
+  </si>
+  <si>
+    <t>Это можно изменить в любой момент: Настройки → Уведомления.</t>
+  </si>
+  <si>
+    <t>onboarding.push.allow</t>
+  </si>
+  <si>
+    <t>Turn on notifications</t>
+  </si>
+  <si>
+    <t>Включить уведомления</t>
+  </si>
+  <si>
+    <t>onboarding.push.later</t>
+  </si>
+  <si>
+    <t>Not now</t>
+  </si>
+  <si>
+    <t>Не сейчас</t>
+  </si>
+  <si>
+    <t>onboarding.verification.title</t>
+  </si>
+  <si>
+    <t>Verification &amp; subscription</t>
+  </si>
+  <si>
+    <t>Верификация и подписка</t>
+  </si>
+  <si>
+    <t>onboarding.verification.subtitle</t>
+  </si>
+  <si>
+    <t>Two more steps before you can send offers. Your 7-day trial starts only after verification is approved — no card needed until then.</t>
+  </si>
+  <si>
+    <t>Ещё два шага до отправки предложений. 7-дневный триал начнётся только после одобрения верификации — до этого карта не нужна.</t>
+  </si>
+  <si>
+    <t>onboarding.verification.item.profile</t>
+  </si>
+  <si>
+    <t>Profile completed</t>
+  </si>
+  <si>
+    <t>Профиль заполнен</t>
+  </si>
+  <si>
+    <t>onboarding.verification.item.license</t>
+  </si>
+  <si>
+    <t>License &amp; identity verification</t>
+  </si>
+  <si>
+    <t>Верификация лицензии и личности</t>
+  </si>
+  <si>
+    <t>onboarding.verification.item.license.desc</t>
+  </si>
+  <si>
+    <t>Bar license number and a quick identity check.</t>
+  </si>
+  <si>
+    <t>Номер лицензии адвоката и быстрая проверка личности.</t>
+  </si>
+  <si>
+    <t>onboarding.verification.item.subscription</t>
+  </si>
+  <si>
+    <t>Subscription: 7-day free trial</t>
+  </si>
+  <si>
+    <t>Подписка: 7 дней бесплатно</t>
+  </si>
+  <si>
+    <t>onboarding.verification.item.subscription.desc</t>
+  </si>
+  <si>
+    <t>Starts after approval. A card is required when the trial starts.</t>
+  </si>
+  <si>
+    <t>Начнётся после одобрения. При старте триала нужна карта.</t>
+  </si>
+  <si>
+    <t>onboarding.verification.status.done</t>
+  </si>
+  <si>
+    <t>onboarding.verification.status.next</t>
+  </si>
+  <si>
+    <t>Next step</t>
+  </si>
+  <si>
+    <t>Следующий шаг</t>
+  </si>
+  <si>
+    <t>onboarding.verification.status.locked</t>
+  </si>
+  <si>
+    <t>After verification</t>
+  </si>
+  <si>
+    <t>После верификации</t>
+  </si>
+  <si>
+    <t>onboarding.verification.verifyNow</t>
+  </si>
+  <si>
+    <t>Verify now</t>
+  </si>
+  <si>
+    <t>Пройти верификацию сейчас</t>
+  </si>
+  <si>
+    <t>onboarding.verification.later</t>
+  </si>
+  <si>
+    <t>Later</t>
+  </si>
+  <si>
+    <t>Позже</t>
+  </si>
+  <si>
+    <t>verification.placeholder.title</t>
+  </si>
+  <si>
+    <t>Verification</t>
+  </si>
+  <si>
+    <t>Верификация</t>
+  </si>
+  <si>
+    <t>verification.placeholder.heading</t>
+  </si>
+  <si>
+    <t>verification.placeholder.body</t>
+  </si>
+  <si>
+    <t>License and identity verification will be available in an upcoming update. We'll notify you when it's ready.</t>
+  </si>
+  <si>
+    <t>Верификация лицензии и личности появится в ближайшем обновлении. Мы сообщим, когда она станет доступна.</t>
+  </si>
+  <si>
+    <t>mine.verification.title</t>
+  </si>
+  <si>
+    <t>Verify your license to see cases</t>
+  </si>
+  <si>
+    <t>Подтвердите лицензию, чтобы видеть кейсы</t>
+  </si>
+  <si>
+    <t>mine.verification.body</t>
+  </si>
+  <si>
+    <t>Cases open up after your license and identity are verified. Feed, Search and Profile are available now.</t>
+  </si>
+  <si>
+    <t>Кейсы станут доступны после верификации лицензии и личности. Лента, Поиск и Профиль уже доступны.</t>
+  </si>
+  <si>
+    <t>onboarding.tour.skip</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>Пропустить</t>
+  </si>
+  <si>
+    <t>onboarding.tour.next</t>
+  </si>
+  <si>
+    <t>Next</t>
+  </si>
+  <si>
+    <t>Далее</t>
+  </si>
+  <si>
+    <t>onboarding.tour.start</t>
+  </si>
+  <si>
+    <t>Get started</t>
+  </si>
+  <si>
+    <t>Начать</t>
+  </si>
+  <si>
+    <t>onboarding.tour.client.1.title</t>
+  </si>
+  <si>
+    <t>Describe your case</t>
+  </si>
+  <si>
+    <t>Опишите кейс</t>
+  </si>
+  <si>
+    <t>onboarding.tour.client.1.body</t>
+  </si>
+  <si>
+    <t>Tell us what happened in plain words. Your contacts stay hidden.</t>
+  </si>
+  <si>
+    <t>Расскажите, что случилось, простыми словами. Ваши контакты скрыты.</t>
+  </si>
+  <si>
+    <t>onboarding.tour.client.2.title</t>
+  </si>
+  <si>
+    <t>Get offers</t>
+  </si>
+  <si>
+    <t>Получите предложения</t>
+  </si>
+  <si>
+    <t>onboarding.tour.client.2.body</t>
+  </si>
+  <si>
+    <t>Verified attorneys licensed in your state send you their offers.</t>
+  </si>
+  <si>
+    <t>Проверенные адвокаты с лицензией в вашем штате пришлют свои предложения.</t>
+  </si>
+  <si>
+    <t>onboarding.tour.client.3.title</t>
+  </si>
+  <si>
+    <t>Choose your attorney</t>
+  </si>
+  <si>
+    <t>Выберите адвоката</t>
+  </si>
+  <si>
+    <t>onboarding.tour.client.3.body</t>
+  </si>
+  <si>
+    <t>Compare offers, chat, and pick the best fit.</t>
+  </si>
+  <si>
+    <t>Сравните предложения, пообщайтесь и выберите лучшего.</t>
+  </si>
+  <si>
+    <t>onboarding.tour.attorney.1.title</t>
+  </si>
+  <si>
+    <t>Verify your license</t>
+  </si>
+  <si>
+    <t>Подтвердите лицензию</t>
+  </si>
+  <si>
+    <t>onboarding.tour.attorney.1.body</t>
+  </si>
+  <si>
+    <t>A quick check of your bar license and identity builds client trust.</t>
+  </si>
+  <si>
+    <t>Быстрая проверка лицензии и личности вызывает доверие клиентов.</t>
+  </si>
+  <si>
+    <t>onboarding.tour.attorney.2.title</t>
+  </si>
+  <si>
+    <t>Browse cases</t>
+  </si>
+  <si>
+    <t>Смотрите кейсы</t>
+  </si>
+  <si>
+    <t>onboarding.tour.attorney.2.body</t>
+  </si>
+  <si>
+    <t>See new cases in your practice areas and the states where you're licensed.</t>
+  </si>
+  <si>
+    <t>Новые кейсы по вашим практикам и штатам, где у вас есть лицензия.</t>
+  </si>
+  <si>
+    <t>onboarding.tour.attorney.3.title</t>
+  </si>
+  <si>
+    <t>Send offers</t>
+  </si>
+  <si>
+    <t>Отправляйте предложения</t>
+  </si>
+  <si>
+    <t>onboarding.tour.attorney.3.body</t>
+  </si>
+  <si>
+    <t>Make your offer — client contacts open once they accept it.</t>
+  </si>
+  <si>
+    <t>Сделайте предложение — контакты клиента откроются после его принятия.</t>
+  </si>
+  <si>
+    <t>settings.downloadData</t>
+  </si>
+  <si>
+    <t>Download my data</t>
+  </si>
+  <si>
+    <t>Скачать мои данные</t>
+  </si>
+  <si>
+    <t>settings.downloadData.stub</t>
+  </si>
+  <si>
+    <t>Data export is coming soon — we'll email you a download link when it's ready.</t>
+  </si>
+  <si>
+    <t>Выгрузка данных скоро появится — ссылка на скачивание придёт на email.</t>
+  </si>
+  <si>
+    <t>onboarding.profile.realNameHint.attorney</t>
+  </si>
+  <si>
+    <t>Clients see your full name on your profile — use the name on your license.</t>
+  </si>
+  <si>
+    <t>Клиенты видят ваше полное имя в профиле — укажите его как в лицензии.</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +2676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2804,6 +4058,1645 @@
         <v>344</v>
       </c>
     </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>345</v>
+      </c>
+      <c r="B126" t="s">
+        <v>346</v>
+      </c>
+      <c r="C126" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>348</v>
+      </c>
+      <c r="B127" t="s">
+        <v>349</v>
+      </c>
+      <c r="C127" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>351</v>
+      </c>
+      <c r="B128" t="s">
+        <v>352</v>
+      </c>
+      <c r="C128" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>354</v>
+      </c>
+      <c r="B129" t="s">
+        <v>355</v>
+      </c>
+      <c r="C129" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>357</v>
+      </c>
+      <c r="B130" t="s">
+        <v>358</v>
+      </c>
+      <c r="C130" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>360</v>
+      </c>
+      <c r="B131" t="s">
+        <v>255</v>
+      </c>
+      <c r="C131" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>361</v>
+      </c>
+      <c r="B132" t="s">
+        <v>362</v>
+      </c>
+      <c r="C132" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>364</v>
+      </c>
+      <c r="B133" t="s">
+        <v>365</v>
+      </c>
+      <c r="C133" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>366</v>
+      </c>
+      <c r="B134" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>368</v>
+      </c>
+      <c r="B135" t="s">
+        <v>369</v>
+      </c>
+      <c r="C135" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>371</v>
+      </c>
+      <c r="B136" t="s">
+        <v>372</v>
+      </c>
+      <c r="C136" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>374</v>
+      </c>
+      <c r="B137" t="s">
+        <v>375</v>
+      </c>
+      <c r="C137" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>377</v>
+      </c>
+      <c r="B138" t="s">
+        <v>378</v>
+      </c>
+      <c r="C138" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>379</v>
+      </c>
+      <c r="B139" t="s">
+        <v>380</v>
+      </c>
+      <c r="C139" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>382</v>
+      </c>
+      <c r="B140" t="s">
+        <v>383</v>
+      </c>
+      <c r="C140" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>385</v>
+      </c>
+      <c r="B141" t="s">
+        <v>386</v>
+      </c>
+      <c r="C141" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>388</v>
+      </c>
+      <c r="B142" t="s">
+        <v>389</v>
+      </c>
+      <c r="C142" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>391</v>
+      </c>
+      <c r="B143" t="s">
+        <v>392</v>
+      </c>
+      <c r="C143" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>394</v>
+      </c>
+      <c r="B144" t="s">
+        <v>395</v>
+      </c>
+      <c r="C144" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>397</v>
+      </c>
+      <c r="B145" t="s">
+        <v>398</v>
+      </c>
+      <c r="C145" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>400</v>
+      </c>
+      <c r="B146" t="s">
+        <v>401</v>
+      </c>
+      <c r="C146" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>403</v>
+      </c>
+      <c r="B147" t="s">
+        <v>404</v>
+      </c>
+      <c r="C147" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>406</v>
+      </c>
+      <c r="B148" t="s">
+        <v>407</v>
+      </c>
+      <c r="C148" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>409</v>
+      </c>
+      <c r="B149" t="s">
+        <v>410</v>
+      </c>
+      <c r="C149" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>412</v>
+      </c>
+      <c r="B150" t="s">
+        <v>413</v>
+      </c>
+      <c r="C150" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>415</v>
+      </c>
+      <c r="B151" t="s">
+        <v>416</v>
+      </c>
+      <c r="C151" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>418</v>
+      </c>
+      <c r="B152" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>421</v>
+      </c>
+      <c r="B153" t="s">
+        <v>422</v>
+      </c>
+      <c r="C153" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>424</v>
+      </c>
+      <c r="B154" t="s">
+        <v>425</v>
+      </c>
+      <c r="C154" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>427</v>
+      </c>
+      <c r="B155" t="s">
+        <v>428</v>
+      </c>
+      <c r="C155" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>430</v>
+      </c>
+      <c r="B156" t="s">
+        <v>431</v>
+      </c>
+      <c r="C156" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>433</v>
+      </c>
+      <c r="B157" t="s">
+        <v>434</v>
+      </c>
+      <c r="C157" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>436</v>
+      </c>
+      <c r="B158" t="s">
+        <v>437</v>
+      </c>
+      <c r="C158" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>439</v>
+      </c>
+      <c r="B159" t="s">
+        <v>440</v>
+      </c>
+      <c r="C159" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>442</v>
+      </c>
+      <c r="B160" t="s">
+        <v>443</v>
+      </c>
+      <c r="C160" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>445</v>
+      </c>
+      <c r="B161" t="s">
+        <v>58</v>
+      </c>
+      <c r="C161" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>446</v>
+      </c>
+      <c r="B162" t="s">
+        <v>46</v>
+      </c>
+      <c r="C162" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>447</v>
+      </c>
+      <c r="B163" t="s">
+        <v>55</v>
+      </c>
+      <c r="C163" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>448</v>
+      </c>
+      <c r="B164" t="s">
+        <v>166</v>
+      </c>
+      <c r="C164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>449</v>
+      </c>
+      <c r="B165" t="s">
+        <v>450</v>
+      </c>
+      <c r="C165" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>452</v>
+      </c>
+      <c r="B166" t="s">
+        <v>453</v>
+      </c>
+      <c r="C166" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>455</v>
+      </c>
+      <c r="B167" t="s">
+        <v>456</v>
+      </c>
+      <c r="C167" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>458</v>
+      </c>
+      <c r="B168" t="s">
+        <v>459</v>
+      </c>
+      <c r="C168" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>461</v>
+      </c>
+      <c r="B169" t="s">
+        <v>462</v>
+      </c>
+      <c r="C169" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>464</v>
+      </c>
+      <c r="B170" t="s">
+        <v>465</v>
+      </c>
+      <c r="C170" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>467</v>
+      </c>
+      <c r="B171" t="s">
+        <v>468</v>
+      </c>
+      <c r="C171" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>470</v>
+      </c>
+      <c r="B172" t="s">
+        <v>471</v>
+      </c>
+      <c r="C172" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>473</v>
+      </c>
+      <c r="B173" t="s">
+        <v>474</v>
+      </c>
+      <c r="C173" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>476</v>
+      </c>
+      <c r="B174" t="s">
+        <v>477</v>
+      </c>
+      <c r="C174" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>479</v>
+      </c>
+      <c r="B175" t="s">
+        <v>480</v>
+      </c>
+      <c r="C175" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>482</v>
+      </c>
+      <c r="B176" t="s">
+        <v>483</v>
+      </c>
+      <c r="C176" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>485</v>
+      </c>
+      <c r="B177" t="s">
+        <v>486</v>
+      </c>
+      <c r="C177" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>488</v>
+      </c>
+      <c r="B178" t="s">
+        <v>489</v>
+      </c>
+      <c r="C178" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>491</v>
+      </c>
+      <c r="B179" t="s">
+        <v>492</v>
+      </c>
+      <c r="C179" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>494</v>
+      </c>
+      <c r="B180" t="s">
+        <v>495</v>
+      </c>
+      <c r="C180" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>496</v>
+      </c>
+      <c r="B181" t="s">
+        <v>34</v>
+      </c>
+      <c r="C181" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>498</v>
+      </c>
+      <c r="B182" t="s">
+        <v>499</v>
+      </c>
+      <c r="C182" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>501</v>
+      </c>
+      <c r="B183" t="s">
+        <v>502</v>
+      </c>
+      <c r="C183" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>504</v>
+      </c>
+      <c r="B184" t="s">
+        <v>505</v>
+      </c>
+      <c r="C184" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>507</v>
+      </c>
+      <c r="B185" t="s">
+        <v>508</v>
+      </c>
+      <c r="C185" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>510</v>
+      </c>
+      <c r="B186" t="s">
+        <v>511</v>
+      </c>
+      <c r="C186" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>513</v>
+      </c>
+      <c r="B187" t="s">
+        <v>514</v>
+      </c>
+      <c r="C187" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>516</v>
+      </c>
+      <c r="B188" t="s">
+        <v>517</v>
+      </c>
+      <c r="C188" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>519</v>
+      </c>
+      <c r="B189" t="s">
+        <v>520</v>
+      </c>
+      <c r="C189" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>522</v>
+      </c>
+      <c r="B190" t="s">
+        <v>523</v>
+      </c>
+      <c r="C190" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>525</v>
+      </c>
+      <c r="B191" t="s">
+        <v>526</v>
+      </c>
+      <c r="C191" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>528</v>
+      </c>
+      <c r="B192" t="s">
+        <v>529</v>
+      </c>
+      <c r="C192" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>531</v>
+      </c>
+      <c r="B193" t="s">
+        <v>22</v>
+      </c>
+      <c r="C193" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>533</v>
+      </c>
+      <c r="B194" t="s">
+        <v>534</v>
+      </c>
+      <c r="C194" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>535</v>
+      </c>
+      <c r="B195" t="s">
+        <v>536</v>
+      </c>
+      <c r="C195" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>538</v>
+      </c>
+      <c r="B196" t="s">
+        <v>539</v>
+      </c>
+      <c r="C196" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>541</v>
+      </c>
+      <c r="B197" t="s">
+        <v>542</v>
+      </c>
+      <c r="C197" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>544</v>
+      </c>
+      <c r="B198" t="s">
+        <v>462</v>
+      </c>
+      <c r="C198" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>545</v>
+      </c>
+      <c r="B199" t="s">
+        <v>546</v>
+      </c>
+      <c r="C199" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>548</v>
+      </c>
+      <c r="B200" t="s">
+        <v>136</v>
+      </c>
+      <c r="C200" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>549</v>
+      </c>
+      <c r="B201" t="s">
+        <v>550</v>
+      </c>
+      <c r="C201" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>552</v>
+      </c>
+      <c r="B202" t="s">
+        <v>553</v>
+      </c>
+      <c r="C202" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>555</v>
+      </c>
+      <c r="B203" t="s">
+        <v>556</v>
+      </c>
+      <c r="C203" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>558</v>
+      </c>
+      <c r="B204" t="s">
+        <v>559</v>
+      </c>
+      <c r="C204" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>561</v>
+      </c>
+      <c r="B205" t="s">
+        <v>562</v>
+      </c>
+      <c r="C205" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>564</v>
+      </c>
+      <c r="B206" t="s">
+        <v>565</v>
+      </c>
+      <c r="C206" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>567</v>
+      </c>
+      <c r="B207" t="s">
+        <v>568</v>
+      </c>
+      <c r="C207" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>570</v>
+      </c>
+      <c r="B208" t="s">
+        <v>571</v>
+      </c>
+      <c r="C208" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>573</v>
+      </c>
+      <c r="B209" t="s">
+        <v>574</v>
+      </c>
+      <c r="C209" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>576</v>
+      </c>
+      <c r="B210" t="s">
+        <v>577</v>
+      </c>
+      <c r="C210" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>579</v>
+      </c>
+      <c r="B211" t="s">
+        <v>580</v>
+      </c>
+      <c r="C211" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>582</v>
+      </c>
+      <c r="B212" t="s">
+        <v>583</v>
+      </c>
+      <c r="C212" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>585</v>
+      </c>
+      <c r="B213" t="s">
+        <v>586</v>
+      </c>
+      <c r="C213" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>588</v>
+      </c>
+      <c r="B214" t="s">
+        <v>589</v>
+      </c>
+      <c r="C214" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>591</v>
+      </c>
+      <c r="B215" t="s">
+        <v>592</v>
+      </c>
+      <c r="C215" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>594</v>
+      </c>
+      <c r="B216" t="s">
+        <v>595</v>
+      </c>
+      <c r="C216" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>597</v>
+      </c>
+      <c r="B217" t="s">
+        <v>598</v>
+      </c>
+      <c r="C217" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>600</v>
+      </c>
+      <c r="B218" t="s">
+        <v>601</v>
+      </c>
+      <c r="C218" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>603</v>
+      </c>
+      <c r="B219" t="s">
+        <v>604</v>
+      </c>
+      <c r="C219" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>606</v>
+      </c>
+      <c r="B220" t="s">
+        <v>607</v>
+      </c>
+      <c r="C220" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>609</v>
+      </c>
+      <c r="B221" t="s">
+        <v>610</v>
+      </c>
+      <c r="C221" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>612</v>
+      </c>
+      <c r="B222" t="s">
+        <v>613</v>
+      </c>
+      <c r="C222" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>615</v>
+      </c>
+      <c r="B223" t="s">
+        <v>616</v>
+      </c>
+      <c r="C223" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>618</v>
+      </c>
+      <c r="B224" t="s">
+        <v>619</v>
+      </c>
+      <c r="C224" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>620</v>
+      </c>
+      <c r="B225" t="s">
+        <v>534</v>
+      </c>
+      <c r="C225" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>621</v>
+      </c>
+      <c r="B226" t="s">
+        <v>622</v>
+      </c>
+      <c r="C226" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>624</v>
+      </c>
+      <c r="B227" t="s">
+        <v>625</v>
+      </c>
+      <c r="C227" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>627</v>
+      </c>
+      <c r="B228" t="s">
+        <v>628</v>
+      </c>
+      <c r="C228" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>630</v>
+      </c>
+      <c r="B229" t="s">
+        <v>631</v>
+      </c>
+      <c r="C229" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>633</v>
+      </c>
+      <c r="B230" t="s">
+        <v>462</v>
+      </c>
+      <c r="C230" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>635</v>
+      </c>
+      <c r="B231" t="s">
+        <v>636</v>
+      </c>
+      <c r="C231" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>638</v>
+      </c>
+      <c r="B232" t="s">
+        <v>639</v>
+      </c>
+      <c r="C232" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>641</v>
+      </c>
+      <c r="B233" t="s">
+        <v>642</v>
+      </c>
+      <c r="C233" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>644</v>
+      </c>
+      <c r="B234" t="s">
+        <v>645</v>
+      </c>
+      <c r="C234" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>647</v>
+      </c>
+      <c r="B235" t="s">
+        <v>648</v>
+      </c>
+      <c r="C235" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>650</v>
+      </c>
+      <c r="B236" t="s">
+        <v>651</v>
+      </c>
+      <c r="C236" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>653</v>
+      </c>
+      <c r="B237" t="s">
+        <v>654</v>
+      </c>
+      <c r="C237" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>656</v>
+      </c>
+      <c r="B238" t="s">
+        <v>657</v>
+      </c>
+      <c r="C238" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>659</v>
+      </c>
+      <c r="B239" t="s">
+        <v>660</v>
+      </c>
+      <c r="C239" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>662</v>
+      </c>
+      <c r="B240" t="s">
+        <v>663</v>
+      </c>
+      <c r="C240" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>665</v>
+      </c>
+      <c r="B241" t="s">
+        <v>666</v>
+      </c>
+      <c r="C241" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>668</v>
+      </c>
+      <c r="B242" t="s">
+        <v>669</v>
+      </c>
+      <c r="C242" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>671</v>
+      </c>
+      <c r="B243" t="s">
+        <v>672</v>
+      </c>
+      <c r="C243" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>674</v>
+      </c>
+      <c r="B244" t="s">
+        <v>675</v>
+      </c>
+      <c r="C244" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>677</v>
+      </c>
+      <c r="B245" t="s">
+        <v>678</v>
+      </c>
+      <c r="C245" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>680</v>
+      </c>
+      <c r="B246" t="s">
+        <v>681</v>
+      </c>
+      <c r="C246" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>683</v>
+      </c>
+      <c r="B247" t="s">
+        <v>355</v>
+      </c>
+      <c r="C247" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>684</v>
+      </c>
+      <c r="B248" t="s">
+        <v>685</v>
+      </c>
+      <c r="C248" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>687</v>
+      </c>
+      <c r="B249" t="s">
+        <v>688</v>
+      </c>
+      <c r="C249" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>690</v>
+      </c>
+      <c r="B250" t="s">
+        <v>691</v>
+      </c>
+      <c r="C250" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>693</v>
+      </c>
+      <c r="B251" t="s">
+        <v>694</v>
+      </c>
+      <c r="C251" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>696</v>
+      </c>
+      <c r="B252" t="s">
+        <v>697</v>
+      </c>
+      <c r="C252" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>699</v>
+      </c>
+      <c r="B253" t="s">
+        <v>231</v>
+      </c>
+      <c r="C253" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>700</v>
+      </c>
+      <c r="B254" t="s">
+        <v>701</v>
+      </c>
+      <c r="C254" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>703</v>
+      </c>
+      <c r="B255" t="s">
+        <v>704</v>
+      </c>
+      <c r="C255" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>706</v>
+      </c>
+      <c r="B256" t="s">
+        <v>707</v>
+      </c>
+      <c r="C256" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>709</v>
+      </c>
+      <c r="B257" t="s">
+        <v>710</v>
+      </c>
+      <c r="C257" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>712</v>
+      </c>
+      <c r="B258" t="s">
+        <v>713</v>
+      </c>
+      <c r="C258" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>715</v>
+      </c>
+      <c r="B259" t="s">
+        <v>716</v>
+      </c>
+      <c r="C259" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>718</v>
+      </c>
+      <c r="B260" t="s">
+        <v>719</v>
+      </c>
+      <c r="C260" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>721</v>
+      </c>
+      <c r="B261" t="s">
+        <v>722</v>
+      </c>
+      <c r="C261" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>724</v>
+      </c>
+      <c r="B262" t="s">
+        <v>725</v>
+      </c>
+      <c r="C262" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>727</v>
+      </c>
+      <c r="B263" t="s">
+        <v>728</v>
+      </c>
+      <c r="C263" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>730</v>
+      </c>
+      <c r="B264" t="s">
+        <v>731</v>
+      </c>
+      <c r="C264" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>733</v>
+      </c>
+      <c r="B265" t="s">
+        <v>734</v>
+      </c>
+      <c r="C265" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>736</v>
+      </c>
+      <c r="B266" t="s">
+        <v>737</v>
+      </c>
+      <c r="C266" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>739</v>
+      </c>
+      <c r="B267" t="s">
+        <v>740</v>
+      </c>
+      <c r="C267" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>742</v>
+      </c>
+      <c r="B268" t="s">
+        <v>743</v>
+      </c>
+      <c r="C268" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>745</v>
+      </c>
+      <c r="B269" t="s">
+        <v>746</v>
+      </c>
+      <c r="C269" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>748</v>
+      </c>
+      <c r="B270" t="s">
+        <v>749</v>
+      </c>
+      <c r="C270" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>751</v>
+      </c>
+      <c r="B271" t="s">
+        <v>752</v>
+      </c>
+      <c r="C271" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>754</v>
+      </c>
+      <c r="B272" t="s">
+        <v>755</v>
+      </c>
+      <c r="C272" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>757</v>
+      </c>
+      <c r="B273" t="s">
+        <v>758</v>
+      </c>
+      <c r="C273" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>760</v>
+      </c>
+      <c r="B274" t="s">
+        <v>761</v>
+      </c>
+      <c r="C274" t="s">
+        <v>762</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="769">
   <si>
     <t>key</t>
   </si>
@@ -2300,6 +2300,24 @@
   </si>
   <si>
     <t>Клиенты видят ваше полное имя в профиле — укажите его как в лицензии.</t>
+  </si>
+  <si>
+    <t>error.api.PHONE_INVALID_US</t>
+  </si>
+  <si>
+    <t>This isn't a valid US number. Check the area code, e.g. (202) 555-1234.</t>
+  </si>
+  <si>
+    <t>Такого номера США нет. Проверьте код города, например (202) 555-1234.</t>
+  </si>
+  <si>
+    <t>error.api.PHONE_TYPE_NOT_ALLOWED</t>
+  </si>
+  <si>
+    <t>We can't text this number. Please use a US mobile number.</t>
+  </si>
+  <si>
+    <t>На этот номер нельзя отправить SMS. Укажите мобильный номер США.</t>
   </si>
 </sst>
 </file>
@@ -2676,7 +2694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C274"/>
+  <dimension ref="A1:C276"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -5697,6 +5715,28 @@
         <v>762</v>
       </c>
     </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>763</v>
+      </c>
+      <c r="B275" t="s">
+        <v>764</v>
+      </c>
+      <c r="C275" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>766</v>
+      </c>
+      <c r="B276" t="s">
+        <v>767</v>
+      </c>
+      <c r="C276" t="s">
+        <v>768</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="942">
   <si>
     <t>key</t>
   </si>
@@ -43,270 +43,273 @@
     <t>auth.otp.submit</t>
   </si>
   <si>
+    <t>Verify</t>
+  </si>
+  <si>
+    <t>Подтвердить</t>
+  </si>
+  <si>
+    <t>auth.otp.subtitle</t>
+  </si>
+  <si>
+    <t>We sent it to {phone}</t>
+  </si>
+  <si>
+    <t>Мы отправили его на {phone}</t>
+  </si>
+  <si>
+    <t>auth.otp.title</t>
+  </si>
+  <si>
+    <t>Enter the code</t>
+  </si>
+  <si>
+    <t>Введите код</t>
+  </si>
+  <si>
+    <t>auth.phone.error.invalid</t>
+  </si>
+  <si>
+    <t>Enter a valid phone number</t>
+  </si>
+  <si>
+    <t>Введите корректный номер телефона</t>
+  </si>
+  <si>
+    <t>auth.phone.fieldLabel</t>
+  </si>
+  <si>
+    <t>Phone number</t>
+  </si>
+  <si>
+    <t>Номер телефона</t>
+  </si>
+  <si>
+    <t>auth.phone.submit</t>
+  </si>
+  <si>
+    <t>Get code</t>
+  </si>
+  <si>
+    <t>Получить код</t>
+  </si>
+  <si>
+    <t>auth.phone.subtitle</t>
+  </si>
+  <si>
+    <t>We'll send a verification code. No password needed.</t>
+  </si>
+  <si>
+    <t>Мы отправим код подтверждения. Пароль не нужен.</t>
+  </si>
+  <si>
+    <t>auth.phone.terms</t>
+  </si>
+  <si>
+    <t>By continuing, you accept the Terms of Use and Privacy Policy</t>
+  </si>
+  <si>
+    <t>Продолжая, вы принимаете Условия использования и Политику конфиденциальности</t>
+  </si>
+  <si>
+    <t>auth.phone.terms.privacy</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
+    <t>Политику конфиденциальности</t>
+  </si>
+  <si>
+    <t>auth.phone.terms.usage</t>
+  </si>
+  <si>
+    <t>Terms of Use</t>
+  </si>
+  <si>
+    <t>Условия использования</t>
+  </si>
+  <si>
+    <t>auth.phone.title</t>
+  </si>
+  <si>
+    <t>Your phone number</t>
+  </si>
+  <si>
+    <t>Ваш номер телефона</t>
+  </si>
+  <si>
+    <t>auth.social.error.accountExists</t>
+  </si>
+  <si>
+    <t>An account with {identifier} already exists. Sign in with: {methods}.</t>
+  </si>
+  <si>
+    <t>Аккаунт с {identifier} уже существует. Войдите через: {methods}.</t>
+  </si>
+  <si>
+    <t>auth.social.error.deleted</t>
+  </si>
+  <si>
+    <t>This account has been deleted.</t>
+  </si>
+  <si>
+    <t>Этот аккаунт был удалён.</t>
+  </si>
+  <si>
+    <t>auth.social.error.invalidToken</t>
+  </si>
+  <si>
+    <t>Couldn't verify sign-in. Please try again.</t>
+  </si>
+  <si>
+    <t>Не удалось подтвердить вход. Попробуйте снова.</t>
+  </si>
+  <si>
+    <t>auth.social.error.network</t>
+  </si>
+  <si>
+    <t>Network error, please try again</t>
+  </si>
+  <si>
+    <t>Ошибка сети, попробуйте снова</t>
+  </si>
+  <si>
+    <t>auth.social.error.providerDisabled</t>
+  </si>
+  <si>
+    <t>This sign-in method is temporarily unavailable.</t>
+  </si>
+  <si>
+    <t>Этот способ входа временно недоступен.</t>
+  </si>
+  <si>
+    <t>auth.social.error.suspended</t>
+  </si>
+  <si>
+    <t>This account has been suspended. Contact support.</t>
+  </si>
+  <si>
+    <t>Аккаунт заблокирован. Обратитесь в поддержку.</t>
+  </si>
+  <si>
+    <t>auth.welcome.apple</t>
+  </si>
+  <si>
+    <t>Continue with Apple</t>
+  </si>
+  <si>
+    <t>Продолжить с Apple</t>
+  </si>
+  <si>
+    <t>auth.welcome.email</t>
+  </si>
+  <si>
+    <t>Continue with email</t>
+  </si>
+  <si>
+    <t>Продолжить с email</t>
+  </si>
+  <si>
+    <t>auth.welcome.google</t>
+  </si>
+  <si>
+    <t>Continue with Google</t>
+  </si>
+  <si>
+    <t>Продолжить с Google</t>
+  </si>
+  <si>
+    <t>auth.welcome.legal</t>
+  </si>
+  <si>
+    <t>LawBid is a bulletin board. We are not a law firm and do not provide legal services. By continuing, you accept the Terms and Privacy Policy.</t>
+  </si>
+  <si>
+    <t>LawBid — доска объявлений. Мы не юридическая фирма и не оказываем юридических услуг. Продолжая, вы принимаете Условия и Политику конфиденциальности.</t>
+  </si>
+  <si>
+    <t>auth.welcome.legal.privacy</t>
+  </si>
+  <si>
+    <t>auth.welcome.legal.terms</t>
+  </si>
+  <si>
+    <t>Terms</t>
+  </si>
+  <si>
+    <t>Условия</t>
+  </si>
+  <si>
+    <t>auth.welcome.notBuiltYet</t>
+  </si>
+  <si>
+    <t>This sign-in method isn't available yet (stage 1.4/1.7)</t>
+  </si>
+  <si>
+    <t>Этот способ входа пока не реализован (этап 1.4/1.7)</t>
+  </si>
+  <si>
+    <t>auth.welcome.phone</t>
+  </si>
+  <si>
+    <t>Continue with phone</t>
+  </si>
+  <si>
+    <t>Продолжить с телефоном</t>
+  </si>
+  <si>
+    <t>auth.welcome.title</t>
+  </si>
+  <si>
+    <t>Bulletin board for clients and attorneys</t>
+  </si>
+  <si>
+    <t>Доска объявлений для клиентов и адвокатов</t>
+  </si>
+  <si>
+    <t>brand.name</t>
+  </si>
+  <si>
+    <t>LawBid</t>
+  </si>
+  <si>
+    <t>brand.pan.left</t>
+  </si>
+  <si>
+    <t>Law</t>
+  </si>
+  <si>
+    <t>brand.pan.right</t>
+  </si>
+  <si>
+    <t>Bid</t>
+  </si>
+  <si>
+    <t>common.back</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>Назад</t>
+  </si>
+  <si>
+    <t>common.cancel</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>Отмена</t>
+  </si>
+  <si>
+    <t>common.confirm</t>
+  </si>
+  <si>
     <t>Confirm</t>
   </si>
   <si>
-    <t>Подтвердить</t>
-  </si>
-  <si>
-    <t>auth.otp.subtitle</t>
-  </si>
-  <si>
-    <t>We sent it to {phone}</t>
-  </si>
-  <si>
-    <t>Мы отправили его на {phone}</t>
-  </si>
-  <si>
-    <t>auth.otp.title</t>
-  </si>
-  <si>
-    <t>Enter the code</t>
-  </si>
-  <si>
-    <t>Введите код</t>
-  </si>
-  <si>
-    <t>auth.phone.error.invalid</t>
-  </si>
-  <si>
-    <t>Enter a valid phone number</t>
-  </si>
-  <si>
-    <t>Введите корректный номер телефона</t>
-  </si>
-  <si>
-    <t>auth.phone.fieldLabel</t>
-  </si>
-  <si>
-    <t>Phone number</t>
-  </si>
-  <si>
-    <t>Номер телефона</t>
-  </si>
-  <si>
-    <t>auth.phone.submit</t>
-  </si>
-  <si>
-    <t>Get code</t>
-  </si>
-  <si>
-    <t>Получить код</t>
-  </si>
-  <si>
-    <t>auth.phone.subtitle</t>
-  </si>
-  <si>
-    <t>We'll text you a verification code. No password needed.</t>
-  </si>
-  <si>
-    <t>Мы отправим код подтверждения. Пароль не нужен.</t>
-  </si>
-  <si>
-    <t>auth.phone.terms</t>
-  </si>
-  <si>
-    <t>By continuing, you agree to the Terms of Use and Privacy Policy</t>
-  </si>
-  <si>
-    <t>Продолжая, вы принимаете Условия использования и Политику конфиденциальности</t>
-  </si>
-  <si>
-    <t>auth.phone.terms.privacy</t>
-  </si>
-  <si>
-    <t>Privacy Policy</t>
-  </si>
-  <si>
-    <t>Политику конфиденциальности</t>
-  </si>
-  <si>
-    <t>auth.phone.terms.usage</t>
-  </si>
-  <si>
-    <t>Terms of Use</t>
-  </si>
-  <si>
-    <t>Условия использования</t>
-  </si>
-  <si>
-    <t>auth.phone.title</t>
-  </si>
-  <si>
-    <t>Your phone number</t>
-  </si>
-  <si>
-    <t>Ваш номер телефона</t>
-  </si>
-  <si>
-    <t>auth.social.error.accountExists</t>
-  </si>
-  <si>
-    <t>An account with {identifier} already exists. Sign in with: {methods}.</t>
-  </si>
-  <si>
-    <t>Аккаунт с {identifier} уже существует. Войдите через: {methods}.</t>
-  </si>
-  <si>
-    <t>auth.social.error.deleted</t>
-  </si>
-  <si>
-    <t>This account has been deleted.</t>
-  </si>
-  <si>
-    <t>Этот аккаунт был удалён.</t>
-  </si>
-  <si>
-    <t>auth.social.error.invalidToken</t>
-  </si>
-  <si>
-    <t>Couldn't verify sign-in. Please try again.</t>
-  </si>
-  <si>
-    <t>Не удалось подтвердить вход. Попробуйте снова.</t>
-  </si>
-  <si>
-    <t>auth.social.error.network</t>
-  </si>
-  <si>
-    <t>Network error, please try again</t>
-  </si>
-  <si>
-    <t>Ошибка сети, попробуйте снова</t>
-  </si>
-  <si>
-    <t>auth.social.error.providerDisabled</t>
-  </si>
-  <si>
-    <t>This sign-in method is temporarily unavailable.</t>
-  </si>
-  <si>
-    <t>Этот способ входа временно недоступен.</t>
-  </si>
-  <si>
-    <t>auth.social.error.suspended</t>
-  </si>
-  <si>
-    <t>This account has been suspended. Contact support.</t>
-  </si>
-  <si>
-    <t>Аккаунт заблокирован. Обратитесь в поддержку.</t>
-  </si>
-  <si>
-    <t>auth.welcome.apple</t>
-  </si>
-  <si>
-    <t>Continue with Apple</t>
-  </si>
-  <si>
-    <t>Продолжить с Apple</t>
-  </si>
-  <si>
-    <t>auth.welcome.email</t>
-  </si>
-  <si>
-    <t>Continue with email</t>
-  </si>
-  <si>
-    <t>Продолжить с email</t>
-  </si>
-  <si>
-    <t>auth.welcome.google</t>
-  </si>
-  <si>
-    <t>Continue with Google</t>
-  </si>
-  <si>
-    <t>Продолжить с Google</t>
-  </si>
-  <si>
-    <t>auth.welcome.legal</t>
-  </si>
-  <si>
-    <t>LawBid is a listings marketplace. We are not a law firm and do not provide legal services. By continuing, you agree to the Terms and Privacy Policy.</t>
-  </si>
-  <si>
-    <t>LawBid — доска объявлений. Мы не юридическая фирма и не оказываем юридических услуг. Продолжая, вы принимаете Условия и Политику конфиденциальности.</t>
-  </si>
-  <si>
-    <t>auth.welcome.legal.privacy</t>
-  </si>
-  <si>
-    <t>auth.welcome.legal.terms</t>
-  </si>
-  <si>
-    <t>Terms</t>
-  </si>
-  <si>
-    <t>Условия</t>
-  </si>
-  <si>
-    <t>auth.welcome.notBuiltYet</t>
-  </si>
-  <si>
-    <t>This sign-in method isn't available yet (stage 1.4/1.7)</t>
-  </si>
-  <si>
-    <t>Этот способ входа пока не реализован (этап 1.4/1.7)</t>
-  </si>
-  <si>
-    <t>auth.welcome.phone</t>
-  </si>
-  <si>
-    <t>Continue with phone</t>
-  </si>
-  <si>
-    <t>Продолжить с телефоном</t>
-  </si>
-  <si>
-    <t>auth.welcome.title</t>
-  </si>
-  <si>
-    <t>A marketplace for clients and attorneys</t>
-  </si>
-  <si>
-    <t>Доска объявлений для клиентов и адвокатов</t>
-  </si>
-  <si>
-    <t>brand.name</t>
-  </si>
-  <si>
-    <t>LawBid</t>
-  </si>
-  <si>
-    <t>brand.pan.left</t>
-  </si>
-  <si>
-    <t>Law</t>
-  </si>
-  <si>
-    <t>brand.pan.right</t>
-  </si>
-  <si>
-    <t>Bid</t>
-  </si>
-  <si>
-    <t>common.back</t>
-  </si>
-  <si>
-    <t>Back</t>
-  </si>
-  <si>
-    <t>Назад</t>
-  </si>
-  <si>
-    <t>common.cancel</t>
-  </si>
-  <si>
-    <t>Cancel</t>
-  </si>
-  <si>
-    <t>Отмена</t>
-  </si>
-  <si>
-    <t>common.confirm</t>
-  </si>
-  <si>
     <t>create.stub.title</t>
   </si>
   <si>
@@ -793,7 +796,7 @@
     <t>onboarding.role.attorney.desc</t>
   </si>
   <si>
-    <t>Licensed attorney: find clients by your practice area and state.</t>
+    <t>Licensed attorney: find clients in your practice areas and states.</t>
   </si>
   <si>
     <t>Лицензированный юрист: находите клиентов по своей практике и штату.</t>
@@ -2318,6 +2321,522 @@
   </si>
   <si>
     <t>На этот номер нельзя отправить SMS. Укажите мобильный номер США.</t>
+  </si>
+  <si>
+    <t>auth.otp.changeNumber</t>
+  </si>
+  <si>
+    <t>Change number</t>
+  </si>
+  <si>
+    <t>Изменить номер</t>
+  </si>
+  <si>
+    <t>auth.otp.changeEmail</t>
+  </si>
+  <si>
+    <t>Change email</t>
+  </si>
+  <si>
+    <t>Изменить email</t>
+  </si>
+  <si>
+    <t>app.update.storeUnavailable</t>
+  </si>
+  <si>
+    <t>The store page isn't available yet. Please update LawBid from the App Store or Google Play.</t>
+  </si>
+  <si>
+    <t>Страница приложения в магазине пока недоступна. Обновите LawBid через App Store или Google Play.</t>
+  </si>
+  <si>
+    <t>app.softUpdate.title</t>
+  </si>
+  <si>
+    <t>A new version is available</t>
+  </si>
+  <si>
+    <t>Доступна новая версия</t>
+  </si>
+  <si>
+    <t>app.softUpdate.message</t>
+  </si>
+  <si>
+    <t>Update LawBid to get the latest improvements.</t>
+  </si>
+  <si>
+    <t>Обновите LawBid, чтобы получить последние улучшения.</t>
+  </si>
+  <si>
+    <t>app.softUpdate.update</t>
+  </si>
+  <si>
+    <t>app.softUpdate.later</t>
+  </si>
+  <si>
+    <t>deeplink.case.title</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>Кейс</t>
+  </si>
+  <si>
+    <t>deeplink.lawyer.title</t>
+  </si>
+  <si>
+    <t>Attorney profile</t>
+  </si>
+  <si>
+    <t>deeplink.post.title</t>
+  </si>
+  <si>
+    <t>Post</t>
+  </si>
+  <si>
+    <t>Публикация</t>
+  </si>
+  <si>
+    <t>deeplink.comingSoon.heading</t>
+  </si>
+  <si>
+    <t>deeplink.comingSoon.body</t>
+  </si>
+  <si>
+    <t>This link will open here as soon as this part of LawBid is available.</t>
+  </si>
+  <si>
+    <t>Эта ссылка будет открываться здесь, как только этот раздел LawBid станет доступен.</t>
+  </si>
+  <si>
+    <t>connectivity.offline</t>
+  </si>
+  <si>
+    <t>No internet connection</t>
+  </si>
+  <si>
+    <t>Нет подключения к интернету</t>
+  </si>
+  <si>
+    <t>connectivity.unreachable</t>
+  </si>
+  <si>
+    <t>Can't reach LawBid right now</t>
+  </si>
+  <si>
+    <t>Сервер LawBid сейчас недоступен</t>
+  </si>
+  <si>
+    <t>connectivity.restored</t>
+  </si>
+  <si>
+    <t>Back online</t>
+  </si>
+  <si>
+    <t>Снова в сети</t>
+  </si>
+  <si>
+    <t>connectivity.checking</t>
+  </si>
+  <si>
+    <t>Checking the connection</t>
+  </si>
+  <si>
+    <t>Проверяем подключение</t>
+  </si>
+  <si>
+    <t>pagination.loadingMore</t>
+  </si>
+  <si>
+    <t>Loading more</t>
+  </si>
+  <si>
+    <t>Загружаем ещё</t>
+  </si>
+  <si>
+    <t>pagination.error</t>
+  </si>
+  <si>
+    <t>Couldn't load more</t>
+  </si>
+  <si>
+    <t>Не удалось загрузить ещё</t>
+  </si>
+  <si>
+    <t>pagination.end</t>
+  </si>
+  <si>
+    <t>That's everything</t>
+  </si>
+  <si>
+    <t>Больше ничего нет</t>
+  </si>
+  <si>
+    <t>feed.empty.title</t>
+  </si>
+  <si>
+    <t>Your feed is empty for now</t>
+  </si>
+  <si>
+    <t>В ленте пока пусто</t>
+  </si>
+  <si>
+    <t>feed.empty.message</t>
+  </si>
+  <si>
+    <t>Posts from attorneys will appear here</t>
+  </si>
+  <si>
+    <t>Здесь появятся посты адвокатов</t>
+  </si>
+  <si>
+    <t>auth.otp.fieldLabel</t>
+  </si>
+  <si>
+    <t>Verification code</t>
+  </si>
+  <si>
+    <t>Код подтверждения</t>
+  </si>
+  <si>
+    <t>account.title</t>
+  </si>
+  <si>
+    <t>account.intro</t>
+  </si>
+  <si>
+    <t>Your contact details and the ways you can sign in to LawBid.</t>
+  </si>
+  <si>
+    <t>Ваши контакты и способы входа в LawBid.</t>
+  </si>
+  <si>
+    <t>account.loading</t>
+  </si>
+  <si>
+    <t>Loading account details</t>
+  </si>
+  <si>
+    <t>Загружаем данные аккаунта</t>
+  </si>
+  <si>
+    <t>account.error</t>
+  </si>
+  <si>
+    <t>Couldn't load your account details.</t>
+  </si>
+  <si>
+    <t>Не удалось загрузить данные аккаунта.</t>
+  </si>
+  <si>
+    <t>account.section.contacts</t>
+  </si>
+  <si>
+    <t>Contact details</t>
+  </si>
+  <si>
+    <t>Контакты</t>
+  </si>
+  <si>
+    <t>account.section.signIn</t>
+  </si>
+  <si>
+    <t>Sign-in methods</t>
+  </si>
+  <si>
+    <t>Способы входа</t>
+  </si>
+  <si>
+    <t>account.section.link</t>
+  </si>
+  <si>
+    <t>Add a sign-in method</t>
+  </si>
+  <si>
+    <t>Добавить способ входа</t>
+  </si>
+  <si>
+    <t>account.contact.phone</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>account.contact.email</t>
+  </si>
+  <si>
+    <t>account.contact.notSet</t>
+  </si>
+  <si>
+    <t>Not added</t>
+  </si>
+  <si>
+    <t>Не добавлен</t>
+  </si>
+  <si>
+    <t>account.contact.change</t>
+  </si>
+  <si>
+    <t>account.contact.add</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>Добавить</t>
+  </si>
+  <si>
+    <t>account.contact.unverified</t>
+  </si>
+  <si>
+    <t>Not verified</t>
+  </si>
+  <si>
+    <t>Не подтверждён</t>
+  </si>
+  <si>
+    <t>account.contacts.reauthHint</t>
+  </si>
+  <si>
+    <t>To change a verified phone or email, first confirm it's you, then enter the code we send to the new contact.</t>
+  </si>
+  <si>
+    <t>Чтобы изменить подтверждённый телефон или email, сначала подтвердите, что это вы, затем введите код, отправленный на новый контакт.</t>
+  </si>
+  <si>
+    <t>account.identifier.phone</t>
+  </si>
+  <si>
+    <t>account.identifier.email</t>
+  </si>
+  <si>
+    <t>account.identifier.apple</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>account.identifier.google</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>account.identifier.primary</t>
+  </si>
+  <si>
+    <t>Primary contact</t>
+  </si>
+  <si>
+    <t>Основной контакт</t>
+  </si>
+  <si>
+    <t>account.identifier.verified</t>
+  </si>
+  <si>
+    <t>account.identifier.linked</t>
+  </si>
+  <si>
+    <t>Connected</t>
+  </si>
+  <si>
+    <t>Подключён</t>
+  </si>
+  <si>
+    <t>account.identifiers.empty</t>
+  </si>
+  <si>
+    <t>No sign-in methods yet.</t>
+  </si>
+  <si>
+    <t>Способов входа пока нет.</t>
+  </si>
+  <si>
+    <t>account.link.phone</t>
+  </si>
+  <si>
+    <t>Add a sign-in phone number</t>
+  </si>
+  <si>
+    <t>Добавить телефон для входа</t>
+  </si>
+  <si>
+    <t>account.link.email</t>
+  </si>
+  <si>
+    <t>Add a sign-in email</t>
+  </si>
+  <si>
+    <t>Добавить email для входа</t>
+  </si>
+  <si>
+    <t>account.link.apple</t>
+  </si>
+  <si>
+    <t>Connect Apple</t>
+  </si>
+  <si>
+    <t>Подключить Apple</t>
+  </si>
+  <si>
+    <t>account.link.google</t>
+  </si>
+  <si>
+    <t>Connect Google</t>
+  </si>
+  <si>
+    <t>Подключить Google</t>
+  </si>
+  <si>
+    <t>account.link.success</t>
+  </si>
+  <si>
+    <t>Sign-in method added</t>
+  </si>
+  <si>
+    <t>Способ входа добавлен</t>
+  </si>
+  <si>
+    <t>account.flow.change.phone.title</t>
+  </si>
+  <si>
+    <t>Change phone number</t>
+  </si>
+  <si>
+    <t>Изменить номер телефона</t>
+  </si>
+  <si>
+    <t>account.flow.change.email.title</t>
+  </si>
+  <si>
+    <t>account.flow.add.phone.title</t>
+  </si>
+  <si>
+    <t>Add phone number</t>
+  </si>
+  <si>
+    <t>Добавить номер телефона</t>
+  </si>
+  <si>
+    <t>account.flow.add.email.title</t>
+  </si>
+  <si>
+    <t>Add email</t>
+  </si>
+  <si>
+    <t>Добавить email</t>
+  </si>
+  <si>
+    <t>account.flow.link.phone.title</t>
+  </si>
+  <si>
+    <t>Sign-in phone number</t>
+  </si>
+  <si>
+    <t>Телефон для входа</t>
+  </si>
+  <si>
+    <t>account.flow.link.email.title</t>
+  </si>
+  <si>
+    <t>Sign-in email</t>
+  </si>
+  <si>
+    <t>Email для входа</t>
+  </si>
+  <si>
+    <t>account.flow.enter.phone</t>
+  </si>
+  <si>
+    <t>Enter the phone number. We'll text it a 6-digit code.</t>
+  </si>
+  <si>
+    <t>Введите номер телефона. Мы отправим на него 6-значный код.</t>
+  </si>
+  <si>
+    <t>account.flow.enter.email</t>
+  </si>
+  <si>
+    <t>Enter the email address. We'll send it a 6-digit code.</t>
+  </si>
+  <si>
+    <t>Введите адрес email. Мы отправим на него 6-значный код.</t>
+  </si>
+  <si>
+    <t>account.flow.sendCode</t>
+  </si>
+  <si>
+    <t>account.flow.identity.title</t>
+  </si>
+  <si>
+    <t>Подтвердите, что это вы</t>
+  </si>
+  <si>
+    <t>account.flow.identity.body</t>
+  </si>
+  <si>
+    <t>We sent a code to {target}. Enter it to continue.</t>
+  </si>
+  <si>
+    <t>Мы отправили код на {target}. Введите его, чтобы продолжить.</t>
+  </si>
+  <si>
+    <t>account.flow.code.title</t>
+  </si>
+  <si>
+    <t>account.flow.code.body</t>
+  </si>
+  <si>
+    <t>We sent a code to {target}.</t>
+  </si>
+  <si>
+    <t>Мы отправили код на {target}.</t>
+  </si>
+  <si>
+    <t>account.flow.editValue</t>
+  </si>
+  <si>
+    <t>Use another</t>
+  </si>
+  <si>
+    <t>Указать другой</t>
+  </si>
+  <si>
+    <t>account.flow.done.title</t>
+  </si>
+  <si>
+    <t>All set</t>
+  </si>
+  <si>
+    <t>account.flow.done.phone</t>
+  </si>
+  <si>
+    <t>Your phone number is verified and saved.</t>
+  </si>
+  <si>
+    <t>Номер телефона подтверждён и сохранён.</t>
+  </si>
+  <si>
+    <t>account.flow.done.email</t>
+  </si>
+  <si>
+    <t>Your email is verified and saved.</t>
+  </si>
+  <si>
+    <t>Email подтверждён и сохранён.</t>
+  </si>
+  <si>
+    <t>account.flow.done.linked</t>
+  </si>
+  <si>
+    <t>You can now sign in with {value}.</t>
+  </si>
+  <si>
+    <t>Теперь вы можете входить с {value}.</t>
+  </si>
+  <si>
+    <t>account.flow.done.action</t>
   </si>
 </sst>
 </file>
@@ -2694,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C276"/>
+  <dimension ref="A1:C344"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3080,7 +3599,7 @@
         <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -3088,128 +3607,128 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
         <v>52</v>
@@ -3220,1250 +3739,1250 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C60" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B62" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B66" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C66" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B69" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B70" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C70" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B71" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C71" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C73" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B74" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C75" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B77" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C78" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B79" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C79" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B80" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C80" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C81" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B82" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C82" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B83" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C83" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B84" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C84" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C85" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B88" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C88" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B89" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C89" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B93" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C93" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B94" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C94" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C95" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C96" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B97" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C97" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B98" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C98" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B100" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C100" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B101" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B102" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B103" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C103" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B104" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C104" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B105" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B106" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C106" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B107" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C107" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B108" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C108" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B109" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C109" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B110" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C110" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B111" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C111" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C112" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B113" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C113" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B114" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C114" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B115" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C115" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B116" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C116" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B117" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C117" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B118" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C118" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B119" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C119" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B120" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B121" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C121" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B122" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C122" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B123" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C123" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B124" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C124" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B125" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C125" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B126" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C126" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B127" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C127" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B128" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C128" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B129" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C129" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B130" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C130" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B131" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B132" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C132" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B133" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C133" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B134" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C134" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B135" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C135" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B136" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C136" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B137" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C137" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B138" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C138" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B139" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C139" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B140" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C140" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B141" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C141" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B142" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C142" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B143" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C143" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C144" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B145" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C145" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B146" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C146" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B147" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C147" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B148" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C148" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B149" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C150" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B151" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C151" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B152" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C152" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B153" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C153" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B154" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C154" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B155" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C155" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B156" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C156" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B157" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C157" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B158" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C158" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B159" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C159" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B160" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C160" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B161" t="s">
         <v>58</v>
@@ -4474,7 +4993,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B162" t="s">
         <v>46</v>
@@ -4485,7 +5004,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B163" t="s">
         <v>55</v>
@@ -4496,186 +5015,186 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B164" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C164" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B165" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C165" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B166" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C166" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B167" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C167" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B168" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C168" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B169" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C169" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B170" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C170" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B171" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C171" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B172" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C172" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B173" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C173" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B174" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C174" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B175" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C175" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B176" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C176" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B177" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C177" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B178" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C178" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B179" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C179" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B180" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C180" t="s">
         <v>38</v>
@@ -4683,1058 +5202,1806 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B181" t="s">
         <v>34</v>
       </c>
       <c r="C181" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B182" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C182" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B183" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C183" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B184" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C184" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B185" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C185" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B186" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C186" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B187" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C187" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B188" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C188" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B189" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C189" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B190" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C190" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B191" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C191" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B192" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C192" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B193" t="s">
         <v>22</v>
       </c>
       <c r="C193" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B194" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C194" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B195" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C195" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B196" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C196" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B197" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C197" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B198" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C198" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B199" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C199" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B200" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C200" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B201" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C201" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B202" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C202" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B203" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C203" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B204" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C204" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B205" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C205" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B206" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C206" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B207" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C207" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B208" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C208" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B209" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C209" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B210" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C210" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B211" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C211" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B212" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C212" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B213" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C213" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B214" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C214" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B215" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C215" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B216" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C216" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B217" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C217" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B218" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C218" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B219" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C219" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B220" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C220" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B221" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C221" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B222" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C222" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B223" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C223" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B224" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C224" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B225" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C225" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B226" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C226" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B227" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C227" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B228" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C228" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B229" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C229" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B230" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C230" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B231" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C231" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B232" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C232" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B233" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C233" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B234" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C234" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B235" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C235" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B236" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C236" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B237" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C237" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B238" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C238" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B239" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C239" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B240" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C240" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B241" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C241" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B242" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C242" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B243" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C243" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B244" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C244" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B245" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C245" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B246" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C246" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B247" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C247" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B248" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C248" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B249" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C249" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B250" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C250" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B251" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C251" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B252" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C252" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B253" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C253" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B254" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C254" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B255" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C255" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B256" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C256" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B257" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C257" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B258" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C258" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B259" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C259" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B260" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C260" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B261" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C261" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B262" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C262" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B263" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C263" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B264" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C264" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B265" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C265" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B266" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C266" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B267" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C267" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B268" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C268" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B269" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C269" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B270" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C270" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B271" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C271" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B272" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C272" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B273" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C273" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B274" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C274" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B275" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C275" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B276" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C276" t="s">
-        <v>768</v>
+        <v>769</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>770</v>
+      </c>
+      <c r="B277" t="s">
+        <v>771</v>
+      </c>
+      <c r="C277" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>773</v>
+      </c>
+      <c r="B278" t="s">
+        <v>774</v>
+      </c>
+      <c r="C278" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>776</v>
+      </c>
+      <c r="B279" t="s">
+        <v>777</v>
+      </c>
+      <c r="C279" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>779</v>
+      </c>
+      <c r="B280" t="s">
+        <v>780</v>
+      </c>
+      <c r="C280" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>782</v>
+      </c>
+      <c r="B281" t="s">
+        <v>783</v>
+      </c>
+      <c r="C281" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>785</v>
+      </c>
+      <c r="B282" t="s">
+        <v>353</v>
+      </c>
+      <c r="C282" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>786</v>
+      </c>
+      <c r="B283" t="s">
+        <v>695</v>
+      </c>
+      <c r="C283" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>787</v>
+      </c>
+      <c r="B284" t="s">
+        <v>788</v>
+      </c>
+      <c r="C284" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>790</v>
+      </c>
+      <c r="B285" t="s">
+        <v>791</v>
+      </c>
+      <c r="C285" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>792</v>
+      </c>
+      <c r="B286" t="s">
+        <v>793</v>
+      </c>
+      <c r="C286" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>795</v>
+      </c>
+      <c r="B287" t="s">
+        <v>232</v>
+      </c>
+      <c r="C287" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>796</v>
+      </c>
+      <c r="B288" t="s">
+        <v>797</v>
+      </c>
+      <c r="C288" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>799</v>
+      </c>
+      <c r="B289" t="s">
+        <v>800</v>
+      </c>
+      <c r="C289" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>802</v>
+      </c>
+      <c r="B290" t="s">
+        <v>803</v>
+      </c>
+      <c r="C290" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>805</v>
+      </c>
+      <c r="B291" t="s">
+        <v>806</v>
+      </c>
+      <c r="C291" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>808</v>
+      </c>
+      <c r="B292" t="s">
+        <v>809</v>
+      </c>
+      <c r="C292" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>811</v>
+      </c>
+      <c r="B293" t="s">
+        <v>812</v>
+      </c>
+      <c r="C293" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>814</v>
+      </c>
+      <c r="B294" t="s">
+        <v>815</v>
+      </c>
+      <c r="C294" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>817</v>
+      </c>
+      <c r="B295" t="s">
+        <v>818</v>
+      </c>
+      <c r="C295" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>820</v>
+      </c>
+      <c r="B296" t="s">
+        <v>821</v>
+      </c>
+      <c r="C296" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>823</v>
+      </c>
+      <c r="B297" t="s">
+        <v>824</v>
+      </c>
+      <c r="C297" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>826</v>
+      </c>
+      <c r="B298" t="s">
+        <v>827</v>
+      </c>
+      <c r="C298" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>829</v>
+      </c>
+      <c r="B299" t="s">
+        <v>282</v>
+      </c>
+      <c r="C299" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>830</v>
+      </c>
+      <c r="B300" t="s">
+        <v>831</v>
+      </c>
+      <c r="C300" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>833</v>
+      </c>
+      <c r="B301" t="s">
+        <v>834</v>
+      </c>
+      <c r="C301" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>836</v>
+      </c>
+      <c r="B302" t="s">
+        <v>837</v>
+      </c>
+      <c r="C302" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>839</v>
+      </c>
+      <c r="B303" t="s">
+        <v>840</v>
+      </c>
+      <c r="C303" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>842</v>
+      </c>
+      <c r="B304" t="s">
+        <v>843</v>
+      </c>
+      <c r="C304" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>845</v>
+      </c>
+      <c r="B305" t="s">
+        <v>846</v>
+      </c>
+      <c r="C305" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>848</v>
+      </c>
+      <c r="B306" t="s">
+        <v>849</v>
+      </c>
+      <c r="C306" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>850</v>
+      </c>
+      <c r="B307" t="s">
+        <v>535</v>
+      </c>
+      <c r="C307" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>851</v>
+      </c>
+      <c r="B308" t="s">
+        <v>852</v>
+      </c>
+      <c r="C308" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>854</v>
+      </c>
+      <c r="B309" t="s">
+        <v>557</v>
+      </c>
+      <c r="C309" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>855</v>
+      </c>
+      <c r="B310" t="s">
+        <v>856</v>
+      </c>
+      <c r="C310" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>858</v>
+      </c>
+      <c r="B311" t="s">
+        <v>859</v>
+      </c>
+      <c r="C311" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>861</v>
+      </c>
+      <c r="B312" t="s">
+        <v>862</v>
+      </c>
+      <c r="C312" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>864</v>
+      </c>
+      <c r="B313" t="s">
+        <v>22</v>
+      </c>
+      <c r="C313" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>865</v>
+      </c>
+      <c r="B314" t="s">
+        <v>535</v>
+      </c>
+      <c r="C314" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>866</v>
+      </c>
+      <c r="B315" t="s">
+        <v>867</v>
+      </c>
+      <c r="C315" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>868</v>
+      </c>
+      <c r="B316" t="s">
+        <v>869</v>
+      </c>
+      <c r="C316" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>870</v>
+      </c>
+      <c r="B317" t="s">
+        <v>871</v>
+      </c>
+      <c r="C317" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>873</v>
+      </c>
+      <c r="B318" t="s">
+        <v>543</v>
+      </c>
+      <c r="C318" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>874</v>
+      </c>
+      <c r="B319" t="s">
+        <v>875</v>
+      </c>
+      <c r="C319" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>877</v>
+      </c>
+      <c r="B320" t="s">
+        <v>878</v>
+      </c>
+      <c r="C320" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>880</v>
+      </c>
+      <c r="B321" t="s">
+        <v>881</v>
+      </c>
+      <c r="C321" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>883</v>
+      </c>
+      <c r="B322" t="s">
+        <v>884</v>
+      </c>
+      <c r="C322" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>886</v>
+      </c>
+      <c r="B323" t="s">
+        <v>887</v>
+      </c>
+      <c r="C323" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>889</v>
+      </c>
+      <c r="B324" t="s">
+        <v>890</v>
+      </c>
+      <c r="C324" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>892</v>
+      </c>
+      <c r="B325" t="s">
+        <v>893</v>
+      </c>
+      <c r="C325" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>895</v>
+      </c>
+      <c r="B326" t="s">
+        <v>896</v>
+      </c>
+      <c r="C326" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>898</v>
+      </c>
+      <c r="B327" t="s">
+        <v>774</v>
+      </c>
+      <c r="C327" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>899</v>
+      </c>
+      <c r="B328" t="s">
+        <v>900</v>
+      </c>
+      <c r="C328" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>902</v>
+      </c>
+      <c r="B329" t="s">
+        <v>903</v>
+      </c>
+      <c r="C329" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>905</v>
+      </c>
+      <c r="B330" t="s">
+        <v>906</v>
+      </c>
+      <c r="C330" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>908</v>
+      </c>
+      <c r="B331" t="s">
+        <v>909</v>
+      </c>
+      <c r="C331" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>911</v>
+      </c>
+      <c r="B332" t="s">
+        <v>912</v>
+      </c>
+      <c r="C332" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>914</v>
+      </c>
+      <c r="B333" t="s">
+        <v>915</v>
+      </c>
+      <c r="C333" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>917</v>
+      </c>
+      <c r="B334" t="s">
+        <v>137</v>
+      </c>
+      <c r="C334" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>918</v>
+      </c>
+      <c r="B335" t="s">
+        <v>143</v>
+      </c>
+      <c r="C335" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>920</v>
+      </c>
+      <c r="B336" t="s">
+        <v>921</v>
+      </c>
+      <c r="C336" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>923</v>
+      </c>
+      <c r="B337" t="s">
+        <v>16</v>
+      </c>
+      <c r="C337" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>924</v>
+      </c>
+      <c r="B338" t="s">
+        <v>925</v>
+      </c>
+      <c r="C338" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>927</v>
+      </c>
+      <c r="B339" t="s">
+        <v>928</v>
+      </c>
+      <c r="C339" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>930</v>
+      </c>
+      <c r="B340" t="s">
+        <v>931</v>
+      </c>
+      <c r="C340" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>932</v>
+      </c>
+      <c r="B341" t="s">
+        <v>933</v>
+      </c>
+      <c r="C341" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>935</v>
+      </c>
+      <c r="B342" t="s">
+        <v>936</v>
+      </c>
+      <c r="C342" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>938</v>
+      </c>
+      <c r="B343" t="s">
+        <v>939</v>
+      </c>
+      <c r="C343" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>941</v>
+      </c>
+      <c r="B344" t="s">
+        <v>356</v>
+      </c>
+      <c r="C344" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="972">
   <si>
     <t>key</t>
   </si>
@@ -2837,6 +2837,96 @@
   </si>
   <si>
     <t>account.flow.done.action</t>
+  </si>
+  <si>
+    <t>error.api.DEVICE_ATTESTATION_REQUIRED</t>
+  </si>
+  <si>
+    <t>We couldn't verify this device. Update the app from the App Store or Google Play and try again.</t>
+  </si>
+  <si>
+    <t>Не удалось проверить устройство. Обновите приложение из App Store или Google Play и попробуйте снова.</t>
+  </si>
+  <si>
+    <t>error.api.AUTH_REFRESH_REUSE_DETECTED</t>
+  </si>
+  <si>
+    <t>For your security, you've been signed out on all devices. Please sign in again.</t>
+  </si>
+  <si>
+    <t>В целях безопасности выполнен выход на всех устройствах. Войдите снова.</t>
+  </si>
+  <si>
+    <t>error.api.AUTH_SESSION_REVOKED</t>
+  </si>
+  <si>
+    <t>Your session has ended. Please sign in again.</t>
+  </si>
+  <si>
+    <t>Сеанс завершён. Войдите снова.</t>
+  </si>
+  <si>
+    <t>error.api.IDEMPOTENCY_KEY_CONFLICT</t>
+  </si>
+  <si>
+    <t>This request is already being processed. Please wait a moment.</t>
+  </si>
+  <si>
+    <t>Запрос уже обрабатывается. Подождите немного.</t>
+  </si>
+  <si>
+    <t>error.api.FORBIDDEN</t>
+  </si>
+  <si>
+    <t>You don't have access to this action.</t>
+  </si>
+  <si>
+    <t>У вас нет доступа к этому действию.</t>
+  </si>
+  <si>
+    <t>error.api.NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Not found. It may have been removed.</t>
+  </si>
+  <si>
+    <t>Не найдено. Возможно, это было удалено.</t>
+  </si>
+  <si>
+    <t>error.api.NOT_IMPLEMENTED</t>
+  </si>
+  <si>
+    <t>This feature isn't available yet.</t>
+  </si>
+  <si>
+    <t>Эта функция пока недоступна.</t>
+  </si>
+  <si>
+    <t>onboarding.consents.age18.desc</t>
+  </si>
+  <si>
+    <t>LawBid is available to adults only.</t>
+  </si>
+  <si>
+    <t>LawBid доступен только совершеннолетним.</t>
+  </si>
+  <si>
+    <t>onboarding.consents.terms.desc</t>
+  </si>
+  <si>
+    <t>You can read the documents below.</t>
+  </si>
+  <si>
+    <t>Документы можно прочитать ниже.</t>
+  </si>
+  <si>
+    <t>onboarding.consents.docs</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Документы</t>
   </si>
 </sst>
 </file>
@@ -3213,7 +3303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C344"/>
+  <dimension ref="A1:C354"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -7004,6 +7094,116 @@
         <v>357</v>
       </c>
     </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>942</v>
+      </c>
+      <c r="B345" t="s">
+        <v>943</v>
+      </c>
+      <c r="C345" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>945</v>
+      </c>
+      <c r="B346" t="s">
+        <v>946</v>
+      </c>
+      <c r="C346" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>948</v>
+      </c>
+      <c r="B347" t="s">
+        <v>949</v>
+      </c>
+      <c r="C347" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>951</v>
+      </c>
+      <c r="B348" t="s">
+        <v>952</v>
+      </c>
+      <c r="C348" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>954</v>
+      </c>
+      <c r="B349" t="s">
+        <v>955</v>
+      </c>
+      <c r="C349" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>957</v>
+      </c>
+      <c r="B350" t="s">
+        <v>958</v>
+      </c>
+      <c r="C350" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>960</v>
+      </c>
+      <c r="B351" t="s">
+        <v>961</v>
+      </c>
+      <c r="C351" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>963</v>
+      </c>
+      <c r="B352" t="s">
+        <v>964</v>
+      </c>
+      <c r="C352" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>966</v>
+      </c>
+      <c r="B353" t="s">
+        <v>967</v>
+      </c>
+      <c r="C353" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>969</v>
+      </c>
+      <c r="B354" t="s">
+        <v>970</v>
+      </c>
+      <c r="C354" t="s">
+        <v>971</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="975">
   <si>
     <t>key</t>
   </si>
@@ -2927,6 +2927,15 @@
   </si>
   <si>
     <t>Документы</t>
+  </si>
+  <si>
+    <t>auth.magicLink.otherDevice</t>
+  </si>
+  <si>
+    <t>Open the link on the phone where you requested the code, or enter the code from the email.</t>
+  </si>
+  <si>
+    <t>Откройте ссылку на телефоне, где вы запрашивали код, или введите код из письма.</t>
   </si>
 </sst>
 </file>
@@ -3303,7 +3312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C354"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -7204,6 +7213,17 @@
         <v>971</v>
       </c>
     </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>972</v>
+      </c>
+      <c r="B355" t="s">
+        <v>973</v>
+      </c>
+      <c r="C355" t="s">
+        <v>974</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="1095">
   <si>
     <t>key</t>
   </si>
@@ -3089,6 +3089,213 @@
   </si>
   <si>
     <t>Загрузка файлов сейчас недоступна. Попробуйте позже.</t>
+  </si>
+  <si>
+    <t>error.api.VERIFICATION_ALREADY_PENDING</t>
+  </si>
+  <si>
+    <t>You already have a verification request. Continue it or wait for the decision.</t>
+  </si>
+  <si>
+    <t>У вас уже есть заявка на верификацию. Продолжите её или дождитесь решения.</t>
+  </si>
+  <si>
+    <t>error.api.VERIFICATION_SUBMISSION_LIMIT</t>
+  </si>
+  <si>
+    <t>Too many requests in the last 30 days. Please try again later.</t>
+  </si>
+  <si>
+    <t>Слишком много заявок за 30 дней. Попробуйте позже.</t>
+  </si>
+  <si>
+    <t>error.api.VERIFICATION_INVALID_STATUS</t>
+  </si>
+  <si>
+    <t>This request can't be changed right now. Please refresh.</t>
+  </si>
+  <si>
+    <t>Сейчас заявку нельзя изменить. Обновите экран.</t>
+  </si>
+  <si>
+    <t>error.api.VERIFICATION_INCOMPLETE</t>
+  </si>
+  <si>
+    <t>Your request is incomplete: add a license with its document, an ID document and a selfie.</t>
+  </si>
+  <si>
+    <t>Заявка не заполнена: нужны лицензия с документом, документ личности и селфи.</t>
+  </si>
+  <si>
+    <t>error.api.LICENSE_ALREADY_REGISTERED</t>
+  </si>
+  <si>
+    <t>This license is already linked to another account. If this is a mistake, contact support.</t>
+  </si>
+  <si>
+    <t>Эта лицензия уже привязана к другому аккаунту. Если это ошибка, обратитесь в поддержку.</t>
+  </si>
+  <si>
+    <t>error.api.LICENSE_ALREADY_ADDED</t>
+  </si>
+  <si>
+    <t>A license for this state is already in your request.</t>
+  </si>
+  <si>
+    <t>Лицензия для этого штата уже добавлена в заявку.</t>
+  </si>
+  <si>
+    <t>error.api.ATTORNEY_SUSPENDED</t>
+  </si>
+  <si>
+    <t>Your profile is suspended. Contact support.</t>
+  </si>
+  <si>
+    <t>Профиль приостановлен. Обратитесь в поддержку.</t>
+  </si>
+  <si>
+    <t>notif.verification.in_review</t>
+  </si>
+  <si>
+    <t>Your verification request is being reviewed.</t>
+  </si>
+  <si>
+    <t>Ваша заявка на верификацию взята в работу.</t>
+  </si>
+  <si>
+    <t>notif.verification.needs_more_info</t>
+  </si>
+  <si>
+    <t>The reviewer needs more information: {message}</t>
+  </si>
+  <si>
+    <t>Проверяющему нужна дополнительная информация: {message}</t>
+  </si>
+  <si>
+    <t>notif.verification.approved</t>
+  </si>
+  <si>
+    <t>You're verified. Choose your practice areas to see cases.</t>
+  </si>
+  <si>
+    <t>Верификация пройдена. Выберите практики, чтобы видеть кейсы.</t>
+  </si>
+  <si>
+    <t>notif.verification.approved_partial</t>
+  </si>
+  <si>
+    <t>You're verified, but some licenses were declined. See the status screen for details.</t>
+  </si>
+  <si>
+    <t>Верификация пройдена частично: часть лицензий отклонена. Подробности на экране статуса.</t>
+  </si>
+  <si>
+    <t>notif.verification.rejected</t>
+  </si>
+  <si>
+    <t>Your verification request was declined. See the status screen for the reason and to apply again.</t>
+  </si>
+  <si>
+    <t>Заявка на верификацию отклонена. Причину и повторную подачу смотрите на экране статуса.</t>
+  </si>
+  <si>
+    <t>notif.verification.suspended</t>
+  </si>
+  <si>
+    <t>Your profile has been suspended. Contact support.</t>
+  </si>
+  <si>
+    <t>Ваш профиль приостановлен. Обратитесь в поддержку.</t>
+  </si>
+  <si>
+    <t>notif.verification.restored</t>
+  </si>
+  <si>
+    <t>Your profile has been restored.</t>
+  </si>
+  <si>
+    <t>Ваш профиль восстановлен.</t>
+  </si>
+  <si>
+    <t>verification.reject.license_not_found</t>
+  </si>
+  <si>
+    <t>License not found in the state database</t>
+  </si>
+  <si>
+    <t>Лицензия не найдена в базе штата</t>
+  </si>
+  <si>
+    <t>verification.reject.license_inactive</t>
+  </si>
+  <si>
+    <t>License is inactive</t>
+  </si>
+  <si>
+    <t>Лицензия неактивна</t>
+  </si>
+  <si>
+    <t>verification.reject.name_mismatch</t>
+  </si>
+  <si>
+    <t>Name doesn't match the documents</t>
+  </si>
+  <si>
+    <t>Имя не совпадает с документами</t>
+  </si>
+  <si>
+    <t>verification.reject.document_unreadable</t>
+  </si>
+  <si>
+    <t>Document is unreadable</t>
+  </si>
+  <si>
+    <t>Документ нечитаем</t>
+  </si>
+  <si>
+    <t>verification.reject.document_expired</t>
+  </si>
+  <si>
+    <t>Document has expired</t>
+  </si>
+  <si>
+    <t>Срок действия документа истёк</t>
+  </si>
+  <si>
+    <t>verification.reject.selfie_mismatch</t>
+  </si>
+  <si>
+    <t>Selfie doesn't match the ID photo</t>
+  </si>
+  <si>
+    <t>Селфи не совпадает с фото в документе</t>
+  </si>
+  <si>
+    <t>verification.reject.suspected_fraud</t>
+  </si>
+  <si>
+    <t>Suspected fraud</t>
+  </si>
+  <si>
+    <t>Подозрение на мошенничество</t>
+  </si>
+  <si>
+    <t>verification.reject.incomplete_submission</t>
+  </si>
+  <si>
+    <t>Request is incomplete</t>
+  </si>
+  <si>
+    <t>Заявка заполнена не полностью</t>
+  </si>
+  <si>
+    <t>verification.reject.other</t>
+  </si>
+  <si>
+    <t>Other reason</t>
+  </si>
+  <si>
+    <t>Другая причина</t>
   </si>
 </sst>
 </file>
@@ -3465,7 +3672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C372"/>
+  <dimension ref="A1:C395"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -7564,6 +7771,259 @@
         <v>1025</v>
       </c>
     </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C374" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C376" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C377" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C378" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C379" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C380" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C381" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B382" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C382" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B383" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C383" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B384" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C384" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C385" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C386" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C387" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C388" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C389" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C390" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C392" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B393" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C393" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C394" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C395" t="s">
+        <v>1094</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="1492">
   <si>
     <t>key</t>
   </si>
@@ -3296,6 +3296,1197 @@
   </si>
   <si>
     <t>Другая причина</t>
+  </si>
+  <si>
+    <t>gate.verify.title</t>
+  </si>
+  <si>
+    <t>Complete verification</t>
+  </si>
+  <si>
+    <t>Пройдите верификацию</t>
+  </si>
+  <si>
+    <t>gate.verify.cta</t>
+  </si>
+  <si>
+    <t>Пройти верификацию</t>
+  </si>
+  <si>
+    <t>gate.verify.cases</t>
+  </si>
+  <si>
+    <t>Cases open after LawBid confirms your license. It usually takes 1–2 business days.</t>
+  </si>
+  <si>
+    <t>Кейсы откроются, когда LawBid подтвердит вашу лицензию. Обычно это 1–2 рабочих дня.</t>
+  </si>
+  <si>
+    <t>gate.verify.post</t>
+  </si>
+  <si>
+    <t>Only verified attorneys can post to the feed, so clients always know who they're reading.</t>
+  </si>
+  <si>
+    <t>Публиковать в ленте могут только верифицированные адвокаты — так клиенты всегда знают, кого читают.</t>
+  </si>
+  <si>
+    <t>gate.verify.postTitle</t>
+  </si>
+  <si>
+    <t>Post to feed</t>
+  </si>
+  <si>
+    <t>Пост в ленту</t>
+  </si>
+  <si>
+    <t>practices.title</t>
+  </si>
+  <si>
+    <t>My practices</t>
+  </si>
+  <si>
+    <t>Мои практики</t>
+  </si>
+  <si>
+    <t>practices.intro</t>
+  </si>
+  <si>
+    <t>Pick the specializations you take cases in. Case matching updates right after you save.</t>
+  </si>
+  <si>
+    <t>Выберите специализации, по которым берёте дела. Подбор кейсов обновится сразу после сохранения.</t>
+  </si>
+  <si>
+    <t>practices.search</t>
+  </si>
+  <si>
+    <t>Search practice areas</t>
+  </si>
+  <si>
+    <t>Поиск по практикам</t>
+  </si>
+  <si>
+    <t>practices.selected</t>
+  </si>
+  <si>
+    <t>Selected ({count})</t>
+  </si>
+  <si>
+    <t>Выбрано ({count})</t>
+  </si>
+  <si>
+    <t>practices.selected.none</t>
+  </si>
+  <si>
+    <t>Nothing selected yet.</t>
+  </si>
+  <si>
+    <t>Пока ничего не выбрано.</t>
+  </si>
+  <si>
+    <t>practices.selectAll</t>
+  </si>
+  <si>
+    <t>Select all</t>
+  </si>
+  <si>
+    <t>Выбрать все</t>
+  </si>
+  <si>
+    <t>practices.clearAll</t>
+  </si>
+  <si>
+    <t>Clear all</t>
+  </si>
+  <si>
+    <t>Снять все</t>
+  </si>
+  <si>
+    <t>practices.pickedCount</t>
+  </si>
+  <si>
+    <t>{count} selected</t>
+  </si>
+  <si>
+    <t>Выбрано: {count}</t>
+  </si>
+  <si>
+    <t>practices.remove</t>
+  </si>
+  <si>
+    <t>Remove {name}</t>
+  </si>
+  <si>
+    <t>Убрать {name}</t>
+  </si>
+  <si>
+    <t>practices.save</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>Сохранить</t>
+  </si>
+  <si>
+    <t>practices.saved</t>
+  </si>
+  <si>
+    <t>Practices saved.</t>
+  </si>
+  <si>
+    <t>Практики сохранены.</t>
+  </si>
+  <si>
+    <t>practices.noResults</t>
+  </si>
+  <si>
+    <t>No practice areas match your search.</t>
+  </si>
+  <si>
+    <t>По запросу ничего не найдено.</t>
+  </si>
+  <si>
+    <t>practices.emptyTree</t>
+  </si>
+  <si>
+    <t>The practice directory is empty right now. Please try again later.</t>
+  </si>
+  <si>
+    <t>Справочник практик сейчас пуст. Попробуйте позже.</t>
+  </si>
+  <si>
+    <t>practices.error</t>
+  </si>
+  <si>
+    <t>Couldn't load practice areas.</t>
+  </si>
+  <si>
+    <t>Не удалось загрузить практики.</t>
+  </si>
+  <si>
+    <t>practices.locked.title</t>
+  </si>
+  <si>
+    <t>Available after verification</t>
+  </si>
+  <si>
+    <t>Доступно после верификации</t>
+  </si>
+  <si>
+    <t>practices.locked.body</t>
+  </si>
+  <si>
+    <t>Practice areas decide which cases you see, so they open once your license is verified.</t>
+  </si>
+  <si>
+    <t>Практики определяют, какие кейсы вы видите, поэтому они открываются после подтверждения лицензии.</t>
+  </si>
+  <si>
+    <t>profile.tab.title</t>
+  </si>
+  <si>
+    <t>profile.attorney.title</t>
+  </si>
+  <si>
+    <t>profile.attorneyChip</t>
+  </si>
+  <si>
+    <t>profile.avatar.label</t>
+  </si>
+  <si>
+    <t>Profile photo</t>
+  </si>
+  <si>
+    <t>Фото профиля</t>
+  </si>
+  <si>
+    <t>profile.verified.label</t>
+  </si>
+  <si>
+    <t>Verified attorney</t>
+  </si>
+  <si>
+    <t>Верифицированный адвокат</t>
+  </si>
+  <si>
+    <t>profile.counters.posts</t>
+  </si>
+  <si>
+    <t>Posts</t>
+  </si>
+  <si>
+    <t>Посты</t>
+  </si>
+  <si>
+    <t>profile.counters.followers</t>
+  </si>
+  <si>
+    <t>Followers</t>
+  </si>
+  <si>
+    <t>Подписчики</t>
+  </si>
+  <si>
+    <t>profile.counters.following</t>
+  </si>
+  <si>
+    <t>Following</t>
+  </si>
+  <si>
+    <t>Подписки</t>
+  </si>
+  <si>
+    <t>profile.rating.new</t>
+  </si>
+  <si>
+    <t>New — no reviews</t>
+  </si>
+  <si>
+    <t>Новый — без отзывов</t>
+  </si>
+  <si>
+    <t>profile.rating.none</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>profile.rating.outOf</t>
+  </si>
+  <si>
+    <t>out of 5</t>
+  </si>
+  <si>
+    <t>из 5</t>
+  </si>
+  <si>
+    <t>profile.rating.count.one</t>
+  </si>
+  <si>
+    <t>{count} review</t>
+  </si>
+  <si>
+    <t>{count} отзыв</t>
+  </si>
+  <si>
+    <t>profile.rating.count.few</t>
+  </si>
+  <si>
+    <t>{count} reviews</t>
+  </si>
+  <si>
+    <t>{count} отзыва</t>
+  </si>
+  <si>
+    <t>profile.rating.count.many</t>
+  </si>
+  <si>
+    <t>{count} отзывов</t>
+  </si>
+  <si>
+    <t>profile.rating.count.other</t>
+  </si>
+  <si>
+    <t>profile.section.firm</t>
+  </si>
+  <si>
+    <t>Firm</t>
+  </si>
+  <si>
+    <t>Фирма</t>
+  </si>
+  <si>
+    <t>profile.section.practices</t>
+  </si>
+  <si>
+    <t>Practice areas</t>
+  </si>
+  <si>
+    <t>Практики</t>
+  </si>
+  <si>
+    <t>profile.section.states</t>
+  </si>
+  <si>
+    <t>Licensed in</t>
+  </si>
+  <si>
+    <t>Лицензии в штатах</t>
+  </si>
+  <si>
+    <t>profile.section.languages</t>
+  </si>
+  <si>
+    <t>Languages</t>
+  </si>
+  <si>
+    <t>Языки</t>
+  </si>
+  <si>
+    <t>profile.practices.group</t>
+  </si>
+  <si>
+    <t>{name} · {count}</t>
+  </si>
+  <si>
+    <t>profile.action.edit</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>Редактировать</t>
+  </si>
+  <si>
+    <t>profile.action.share</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>Поделиться</t>
+  </si>
+  <si>
+    <t>profile.action.follow</t>
+  </si>
+  <si>
+    <t>Follow</t>
+  </si>
+  <si>
+    <t>Подписаться</t>
+  </si>
+  <si>
+    <t>profile.share.copied</t>
+  </si>
+  <si>
+    <t>Profile link copied.</t>
+  </si>
+  <si>
+    <t>Ссылка на профиль скопирована.</t>
+  </si>
+  <si>
+    <t>profile.tab.posts</t>
+  </si>
+  <si>
+    <t>profile.tab.reviews</t>
+  </si>
+  <si>
+    <t>Reviews</t>
+  </si>
+  <si>
+    <t>Отзывы</t>
+  </si>
+  <si>
+    <t>profile.posts.empty.title</t>
+  </si>
+  <si>
+    <t>No posts yet</t>
+  </si>
+  <si>
+    <t>Постов пока нет</t>
+  </si>
+  <si>
+    <t>profile.posts.empty.self</t>
+  </si>
+  <si>
+    <t>Your posts will appear here.</t>
+  </si>
+  <si>
+    <t>Здесь появятся ваши посты.</t>
+  </si>
+  <si>
+    <t>profile.posts.empty.other</t>
+  </si>
+  <si>
+    <t>This attorney hasn't posted yet.</t>
+  </si>
+  <si>
+    <t>Адвокат пока ничего не публиковал.</t>
+  </si>
+  <si>
+    <t>profile.verifyBanner.body</t>
+  </si>
+  <si>
+    <t>Get the blue check and access to cases.</t>
+  </si>
+  <si>
+    <t>Получите синюю галочку и доступ к кейсам.</t>
+  </si>
+  <si>
+    <t>profile.error</t>
+  </si>
+  <si>
+    <t>Couldn't load the profile.</t>
+  </si>
+  <si>
+    <t>Не удалось загрузить профиль.</t>
+  </si>
+  <si>
+    <t>profile.unavailable.title</t>
+  </si>
+  <si>
+    <t>Profile unavailable</t>
+  </si>
+  <si>
+    <t>Профиль недоступен</t>
+  </si>
+  <si>
+    <t>profile.unavailable.body</t>
+  </si>
+  <si>
+    <t>This profile doesn't exist or can't be shown.</t>
+  </si>
+  <si>
+    <t>Такого профиля нет или его нельзя показать.</t>
+  </si>
+  <si>
+    <t>profile.client.noName</t>
+  </si>
+  <si>
+    <t>Your name</t>
+  </si>
+  <si>
+    <t>Ваше имя</t>
+  </si>
+  <si>
+    <t>profile.client.myCases</t>
+  </si>
+  <si>
+    <t>My cases</t>
+  </si>
+  <si>
+    <t>Мои кейсы</t>
+  </si>
+  <si>
+    <t>profile.client.onlyYou</t>
+  </si>
+  <si>
+    <t>Visible only to you</t>
+  </si>
+  <si>
+    <t>Видно только вам</t>
+  </si>
+  <si>
+    <t>profile.client.noCases</t>
+  </si>
+  <si>
+    <t>You have no cases yet</t>
+  </si>
+  <si>
+    <t>У вас пока нет кейсов</t>
+  </si>
+  <si>
+    <t>profile.client.noCases.body</t>
+  </si>
+  <si>
+    <t>Your profile is private: attorneys and other clients can't see it.</t>
+  </si>
+  <si>
+    <t>Ваш профиль закрыт: его не видят ни адвокаты, ни другие клиенты.</t>
+  </si>
+  <si>
+    <t>profile.edit.title</t>
+  </si>
+  <si>
+    <t>Edit profile</t>
+  </si>
+  <si>
+    <t>Редактирование профиля</t>
+  </si>
+  <si>
+    <t>profile.edit.save</t>
+  </si>
+  <si>
+    <t>profile.edit.saved</t>
+  </si>
+  <si>
+    <t>Profile saved.</t>
+  </si>
+  <si>
+    <t>Профиль сохранён.</t>
+  </si>
+  <si>
+    <t>profile.edit.nameRecheck</t>
+  </si>
+  <si>
+    <t>Changing your name sends your profile for a quick re-check so it matches your documents.</t>
+  </si>
+  <si>
+    <t>После смены имени профиль уйдёт на короткую повторную проверку, чтобы имя совпадало с документами.</t>
+  </si>
+  <si>
+    <t>profile.edit.section.practice</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>Практика</t>
+  </si>
+  <si>
+    <t>profile.edit.section.licenses</t>
+  </si>
+  <si>
+    <t>Licenses</t>
+  </si>
+  <si>
+    <t>Лицензии</t>
+  </si>
+  <si>
+    <t>profile.license.pending</t>
+  </si>
+  <si>
+    <t>Under review</t>
+  </si>
+  <si>
+    <t>На проверке</t>
+  </si>
+  <si>
+    <t>profile.license.verified</t>
+  </si>
+  <si>
+    <t>Подтверждена</t>
+  </si>
+  <si>
+    <t>profile.license.rejected</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>Отклонена</t>
+  </si>
+  <si>
+    <t>profile.license.expired</t>
+  </si>
+  <si>
+    <t>Expired</t>
+  </si>
+  <si>
+    <t>Истекла</t>
+  </si>
+  <si>
+    <t>profile.license.suspended</t>
+  </si>
+  <si>
+    <t>Suspended</t>
+  </si>
+  <si>
+    <t>Приостановлена</t>
+  </si>
+  <si>
+    <t>profile.license.unknown</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Неизвестно</t>
+  </si>
+  <si>
+    <t>profile.username.label</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Имя пользователя</t>
+  </si>
+  <si>
+    <t>profile.username.hint</t>
+  </si>
+  <si>
+    <t>3–30 letters, digits, "_" or ".". You can change it once every 30 days.</t>
+  </si>
+  <si>
+    <t>3–30 символов: латиница, цифры, «_» или «.». Менять можно раз в 30 дней.</t>
+  </si>
+  <si>
+    <t>profile.username.cooldown</t>
+  </si>
+  <si>
+    <t>You can change your @username again on {date}.</t>
+  </si>
+  <si>
+    <t>Сменить @username снова можно {date}.</t>
+  </si>
+  <si>
+    <t>profile.username.checking</t>
+  </si>
+  <si>
+    <t>Checking…</t>
+  </si>
+  <si>
+    <t>Проверяем…</t>
+  </si>
+  <si>
+    <t>profile.username.available</t>
+  </si>
+  <si>
+    <t>This @username is available.</t>
+  </si>
+  <si>
+    <t>Этот @username свободен.</t>
+  </si>
+  <si>
+    <t>profile.username.invalid</t>
+  </si>
+  <si>
+    <t>Use 3–30 latin letters, digits, "_" or "."; not at the start or end, no "..".</t>
+  </si>
+  <si>
+    <t>3–30 символов: латиница, цифры, «_» или «.»; не в начале и не в конце, без «..».</t>
+  </si>
+  <si>
+    <t>profile.username.checkFailed</t>
+  </si>
+  <si>
+    <t>Couldn't check availability. We'll check when you save.</t>
+  </si>
+  <si>
+    <t>Не удалось проверить. Проверим при сохранении.</t>
+  </si>
+  <si>
+    <t>profile.photo.label</t>
+  </si>
+  <si>
+    <t>profile.photo.hint</t>
+  </si>
+  <si>
+    <t>A clear business photo. JPEG, PNG or HEIC, up to 5 MB.</t>
+  </si>
+  <si>
+    <t>Чёткое деловое фото. JPEG, PNG или HEIC, до 5 МБ.</t>
+  </si>
+  <si>
+    <t>profile.photo.add</t>
+  </si>
+  <si>
+    <t>Add photo</t>
+  </si>
+  <si>
+    <t>Добавить фото</t>
+  </si>
+  <si>
+    <t>profile.photo.change</t>
+  </si>
+  <si>
+    <t>Change photo</t>
+  </si>
+  <si>
+    <t>Изменить фото</t>
+  </si>
+  <si>
+    <t>profile.photo.camera</t>
+  </si>
+  <si>
+    <t>Take a photo</t>
+  </si>
+  <si>
+    <t>Сделать фото</t>
+  </si>
+  <si>
+    <t>profile.photo.gallery</t>
+  </si>
+  <si>
+    <t>Choose from library</t>
+  </si>
+  <si>
+    <t>Выбрать из галереи</t>
+  </si>
+  <si>
+    <t>profile.photo.preparing</t>
+  </si>
+  <si>
+    <t>Preparing…</t>
+  </si>
+  <si>
+    <t>Подготовка…</t>
+  </si>
+  <si>
+    <t>profile.photo.uploading</t>
+  </si>
+  <si>
+    <t>Uploading… {percent}%</t>
+  </si>
+  <si>
+    <t>Загрузка… {percent}%</t>
+  </si>
+  <si>
+    <t>profile.photo.checking</t>
+  </si>
+  <si>
+    <t>Checking the photo…</t>
+  </si>
+  <si>
+    <t>Проверяем фото…</t>
+  </si>
+  <si>
+    <t>profile.photo.done</t>
+  </si>
+  <si>
+    <t>Photo updated.</t>
+  </si>
+  <si>
+    <t>Фото обновлено.</t>
+  </si>
+  <si>
+    <t>profile.photo.pickFailed</t>
+  </si>
+  <si>
+    <t>Couldn't open the photo. Please try another one.</t>
+  </si>
+  <si>
+    <t>Не удалось открыть фото. Попробуйте другое.</t>
+  </si>
+  <si>
+    <t>contacts.title</t>
+  </si>
+  <si>
+    <t>My contacts</t>
+  </si>
+  <si>
+    <t>Мои контакты</t>
+  </si>
+  <si>
+    <t>contacts.section.confirmed</t>
+  </si>
+  <si>
+    <t>Confirmed contacts</t>
+  </si>
+  <si>
+    <t>Подтверждённые контакты</t>
+  </si>
+  <si>
+    <t>contacts.section.preferences</t>
+  </si>
+  <si>
+    <t>How attorneys can reach you</t>
+  </si>
+  <si>
+    <t>Как с вами связаться</t>
+  </si>
+  <si>
+    <t>contacts.prefs.saved</t>
+  </si>
+  <si>
+    <t>Contact preferences saved.</t>
+  </si>
+  <si>
+    <t>Предпочтения связи сохранены.</t>
+  </si>
+  <si>
+    <t>contacts.prefs.error</t>
+  </si>
+  <si>
+    <t>Couldn't load your contact preferences.</t>
+  </si>
+  <si>
+    <t>Не удалось загрузить предпочтения связи.</t>
+  </si>
+  <si>
+    <t>reviews.author.anonymous</t>
+  </si>
+  <si>
+    <t>LawBid client</t>
+  </si>
+  <si>
+    <t>Клиент LawBid</t>
+  </si>
+  <si>
+    <t>reviews.edited</t>
+  </si>
+  <si>
+    <t>Edited</t>
+  </si>
+  <si>
+    <t>Изменено</t>
+  </si>
+  <si>
+    <t>reviews.stars.label</t>
+  </si>
+  <si>
+    <t>{rating} out of 5 stars</t>
+  </si>
+  <si>
+    <t>{rating} из 5 звёзд</t>
+  </si>
+  <si>
+    <t>reviews.average.label</t>
+  </si>
+  <si>
+    <t>Rating {rating} out of 5</t>
+  </si>
+  <si>
+    <t>Рейтинг {rating} из 5</t>
+  </si>
+  <si>
+    <t>reviews.distribution.row</t>
+  </si>
+  <si>
+    <t>{stars} stars: {count}</t>
+  </si>
+  <si>
+    <t>{stars} звёзд: {count}</t>
+  </si>
+  <si>
+    <t>reviews.end</t>
+  </si>
+  <si>
+    <t>That's all the reviews</t>
+  </si>
+  <si>
+    <t>Это все отзывы</t>
+  </si>
+  <si>
+    <t>reviews.error</t>
+  </si>
+  <si>
+    <t>Couldn't load reviews.</t>
+  </si>
+  <si>
+    <t>Не удалось загрузить отзывы.</t>
+  </si>
+  <si>
+    <t>reviews.empty.self</t>
+  </si>
+  <si>
+    <t>When clients rate your work after a closed case, reviews will appear here.</t>
+  </si>
+  <si>
+    <t>Когда клиенты оценят вашу работу по закрытому кейсу, отзывы появятся здесь.</t>
+  </si>
+  <si>
+    <t>reviews.empty.other</t>
+  </si>
+  <si>
+    <t>This attorney has no reviews yet.</t>
+  </si>
+  <si>
+    <t>У этого адвоката пока нет отзывов.</t>
+  </si>
+  <si>
+    <t>reviews.report.action</t>
+  </si>
+  <si>
+    <t>Report review</t>
+  </si>
+  <si>
+    <t>Пожаловаться на отзыв</t>
+  </si>
+  <si>
+    <t>reviews.report.title</t>
+  </si>
+  <si>
+    <t>Why are you reporting this review?</t>
+  </si>
+  <si>
+    <t>Почему вы жалуетесь на отзыв?</t>
+  </si>
+  <si>
+    <t>reviews.report.sent</t>
+  </si>
+  <si>
+    <t>Thanks. Our moderators will review it.</t>
+  </si>
+  <si>
+    <t>Спасибо. Модераторы рассмотрят жалобу.</t>
+  </si>
+  <si>
+    <t>reviews.report.reason.spam</t>
+  </si>
+  <si>
+    <t>Spam</t>
+  </si>
+  <si>
+    <t>Спам</t>
+  </si>
+  <si>
+    <t>reviews.report.reason.abuse</t>
+  </si>
+  <si>
+    <t>Abuse or harassment</t>
+  </si>
+  <si>
+    <t>Оскорбления или травля</t>
+  </si>
+  <si>
+    <t>reviews.report.reason.misinformation</t>
+  </si>
+  <si>
+    <t>False information</t>
+  </si>
+  <si>
+    <t>Ложная информация</t>
+  </si>
+  <si>
+    <t>reviews.report.reason.impersonation</t>
+  </si>
+  <si>
+    <t>Not a real client</t>
+  </si>
+  <si>
+    <t>Не настоящий клиент</t>
+  </si>
+  <si>
+    <t>reviews.report.reason.inappropriate</t>
+  </si>
+  <si>
+    <t>Inappropriate content</t>
+  </si>
+  <si>
+    <t>Неуместное содержание</t>
+  </si>
+  <si>
+    <t>reviews.report.reason.other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Другое</t>
+  </si>
+  <si>
+    <t>reviews.form.title</t>
+  </si>
+  <si>
+    <t>Rate your attorney</t>
+  </si>
+  <si>
+    <t>Оцените адвоката</t>
+  </si>
+  <si>
+    <t>reviews.form.titleYours</t>
+  </si>
+  <si>
+    <t>Your review</t>
+  </si>
+  <si>
+    <t>Ваш отзыв</t>
+  </si>
+  <si>
+    <t>reviews.form.question</t>
+  </si>
+  <si>
+    <t>How did your attorney handle the case?</t>
+  </si>
+  <si>
+    <t>Как адвокат вёл ваше дело?</t>
+  </si>
+  <si>
+    <t>reviews.form.tapToRate</t>
+  </si>
+  <si>
+    <t>Tap a star to rate</t>
+  </si>
+  <si>
+    <t>Нажмите на звезду, чтобы оценить</t>
+  </si>
+  <si>
+    <t>reviews.form.ratingRequired</t>
+  </si>
+  <si>
+    <t>Please choose a rating</t>
+  </si>
+  <si>
+    <t>Выберите оценку</t>
+  </si>
+  <si>
+    <t>reviews.form.rating.1</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>Плохо</t>
+  </si>
+  <si>
+    <t>reviews.form.rating.2</t>
+  </si>
+  <si>
+    <t>Fair</t>
+  </si>
+  <si>
+    <t>Так себе</t>
+  </si>
+  <si>
+    <t>reviews.form.rating.3</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Хорошо</t>
+  </si>
+  <si>
+    <t>reviews.form.rating.4</t>
+  </si>
+  <si>
+    <t>Very good</t>
+  </si>
+  <si>
+    <t>Очень хорошо</t>
+  </si>
+  <si>
+    <t>reviews.form.rating.5</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Отлично</t>
+  </si>
+  <si>
+    <t>reviews.form.body</t>
+  </si>
+  <si>
+    <t>reviews.form.bodyHint</t>
+  </si>
+  <si>
+    <t>What went well, what could be better</t>
+  </si>
+  <si>
+    <t>Что понравилось, что можно улучшить</t>
+  </si>
+  <si>
+    <t>reviews.form.notice</t>
+  </si>
+  <si>
+    <t>A review can't be deleted. You can edit it within 14 days.</t>
+  </si>
+  <si>
+    <t>Отзыв нельзя удалить, его можно изменить в течение 14 дней.</t>
+  </si>
+  <si>
+    <t>reviews.form.submit</t>
+  </si>
+  <si>
+    <t>Publish review</t>
+  </si>
+  <si>
+    <t>Опубликовать отзыв</t>
+  </si>
+  <si>
+    <t>reviews.form.saveEdit</t>
+  </si>
+  <si>
+    <t>Save changes</t>
+  </si>
+  <si>
+    <t>Сохранить изменения</t>
+  </si>
+  <si>
+    <t>reviews.form.published</t>
+  </si>
+  <si>
+    <t>Review published.</t>
+  </si>
+  <si>
+    <t>Отзыв опубликован.</t>
+  </si>
+  <si>
+    <t>reviews.form.updated</t>
+  </si>
+  <si>
+    <t>Review updated.</t>
+  </si>
+  <si>
+    <t>Отзыв изменён.</t>
+  </si>
+  <si>
+    <t>reviews.form.publishedHeading</t>
+  </si>
+  <si>
+    <t>Your review is published</t>
+  </si>
+  <si>
+    <t>Ваш отзыв опубликован</t>
+  </si>
+  <si>
+    <t>reviews.form.previewHint</t>
+  </si>
+  <si>
+    <t>This is how others see it — your first name and last initial only.</t>
+  </si>
+  <si>
+    <t>Так его видят другие — только имя и первая буква фамилии.</t>
+  </si>
+  <si>
+    <t>reviews.form.edit</t>
+  </si>
+  <si>
+    <t>Edit review</t>
+  </si>
+  <si>
+    <t>Изменить отзыв</t>
+  </si>
+  <si>
+    <t>reviews.form.editableUntil</t>
+  </si>
+  <si>
+    <t>You can edit it until {date}.</t>
+  </si>
+  <si>
+    <t>Изменить можно до {date}.</t>
+  </si>
+  <si>
+    <t>reviews.form.locked</t>
+  </si>
+  <si>
+    <t>The 14-day editing window has ended, so this review can no longer be changed.</t>
+  </si>
+  <si>
+    <t>14 дней на изменение прошли, отзыв больше нельзя изменить.</t>
+  </si>
+  <si>
+    <t>reviews.placeholder.entry</t>
+  </si>
+  <si>
+    <t>Leave a review for a closed case</t>
+  </si>
+  <si>
+    <t>Оставить отзыв по закрытому кейсу</t>
+  </si>
+  <si>
+    <t>reviews.placeholder.body</t>
+  </si>
+  <si>
+    <t>Preview build: closed cases arrive with the cases module. Enter the case ID to open the review form.</t>
+  </si>
+  <si>
+    <t>Тестовая сборка: закрытые кейсы появятся вместе с модулем кейсов. Введите ID кейса, чтобы открыть форму отзыва.</t>
+  </si>
+  <si>
+    <t>reviews.placeholder.caseId</t>
+  </si>
+  <si>
+    <t>Case ID</t>
+  </si>
+  <si>
+    <t>ID кейса</t>
+  </si>
+  <si>
+    <t>error.default.title</t>
+  </si>
+  <si>
+    <t>onboarding.profile.error.photoRequired</t>
+  </si>
+  <si>
+    <t>Add a photo — it is required for attorneys.</t>
+  </si>
+  <si>
+    <t>Добавьте фото — для адвоката оно обязательно.</t>
+  </si>
+  <si>
+    <t>onboarding.role.locked</t>
+  </si>
+  <si>
+    <t>Your role is already set and can't be changed.</t>
+  </si>
+  <si>
+    <t>Роль уже выбрана и не может быть изменена.</t>
   </si>
 </sst>
 </file>
@@ -3672,7 +4863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C395"/>
+  <dimension ref="A1:C535"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -8024,6 +9215,1546 @@
         <v>1094</v>
       </c>
     </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C396" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C397" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C398" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C399" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C400" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C401" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C402" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C403" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C404" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C405" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C406" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C407" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C408" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C409" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C411" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C414" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C416" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B417" t="s">
+        <v>253</v>
+      </c>
+      <c r="C417" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B418" t="s">
+        <v>264</v>
+      </c>
+      <c r="C418" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B419" t="s">
+        <v>264</v>
+      </c>
+      <c r="C419" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C420" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C421" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C422" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C423" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C424" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C425" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C426" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C427" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C429" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C430" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C431" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C432" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C433" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C434" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C435" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C436" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C437" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C438" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C439" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C440" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C441" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C442" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C443" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C444" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C445" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C446" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C447" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C448" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C449" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C450" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C451" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C452" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C453" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C454" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C455" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C456" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C457" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C458" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C459" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C460" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C461" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B462" t="s">
+        <v>543</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C463" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C464" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C465" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C466" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C467" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C468" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C470" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C481" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C486" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C487" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C488" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C489" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C490" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C491" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C492" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C493" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C494" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C495" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C496" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C512" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C514" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C515" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C516" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C517" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C518" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C519" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C521" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C522" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C523" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C527" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C528" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C529" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C532" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B533" t="s">
+        <v>223</v>
+      </c>
+      <c r="C533" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C534" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C535" t="s">
+        <v>1491</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -2032,19 +2032,19 @@
     <t>onboarding.verification.item.license</t>
   </si>
   <si>
-    <t>License &amp; identity verification</t>
-  </si>
-  <si>
-    <t>Верификация лицензии и личности</t>
+    <t>License confirmation</t>
+  </si>
+  <si>
+    <t>Подтверждение лицензии</t>
   </si>
   <si>
     <t>onboarding.verification.item.license.desc</t>
   </si>
   <si>
-    <t>Bar license number and a quick identity check.</t>
-  </si>
-  <si>
-    <t>Номер лицензии адвоката и быстрая проверка личности.</t>
+    <t>Your state and bar number, confirmed with one tick.</t>
+  </si>
+  <si>
+    <t>Штат и номер лицензии — подтверждаете одной галочкой.</t>
   </si>
   <si>
     <t>onboarding.verification.item.subscription</t>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="1909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="2050">
   <si>
     <t>key</t>
   </si>
@@ -5738,6 +5738,429 @@
   </si>
   <si>
     <t>Выбрать практики</t>
+  </si>
+  <si>
+    <t>plan.free</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Бесплатно</t>
+  </si>
+  <si>
+    <t>plan.status.yours</t>
+  </si>
+  <si>
+    <t>Your plan</t>
+  </si>
+  <si>
+    <t>Ваш план</t>
+  </si>
+  <si>
+    <t>plan.pay.trialDays</t>
+  </si>
+  <si>
+    <t>Start {n} days free</t>
+  </si>
+  <si>
+    <t>Начать {n} дней бесплатно</t>
+  </si>
+  <si>
+    <t>plan.f.seatsIncluded</t>
+  </si>
+  <si>
+    <t>Assistants included: {n}</t>
+  </si>
+  <si>
+    <t>Помощников включено: {n}</t>
+  </si>
+  <si>
+    <t>plan.f.extraSeat</t>
+  </si>
+  <si>
+    <t>Extra assistant: {price}/mo</t>
+  </si>
+  <si>
+    <t>Доп. помощник: {price}/мес</t>
+  </si>
+  <si>
+    <t>plan.f.bidsAnyState</t>
+  </si>
+  <si>
+    <t>Offers in any state</t>
+  </si>
+  <si>
+    <t>Ставки в любом штате</t>
+  </si>
+  <si>
+    <t>plan.f.maxActiveBids</t>
+  </si>
+  <si>
+    <t>Active offers: up to {n}</t>
+  </si>
+  <si>
+    <t>Активных ставок: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedBids</t>
+  </si>
+  <si>
+    <t>Unlimited active offers</t>
+  </si>
+  <si>
+    <t>Активные ставки без ограничений</t>
+  </si>
+  <si>
+    <t>plan.f.prioritySearch</t>
+  </si>
+  <si>
+    <t>Higher in search</t>
+  </si>
+  <si>
+    <t>Приоритет в поиске</t>
+  </si>
+  <si>
+    <t>plan.f.videoCalls</t>
+  </si>
+  <si>
+    <t>Video calls</t>
+  </si>
+  <si>
+    <t>Видеозвонки</t>
+  </si>
+  <si>
+    <t>plan.f.documentTemplates</t>
+  </si>
+  <si>
+    <t>Document templates</t>
+  </si>
+  <si>
+    <t>Шаблоны документов</t>
+  </si>
+  <si>
+    <t>plan.f.trial</t>
+  </si>
+  <si>
+    <t>{n}-day free trial</t>
+  </si>
+  <si>
+    <t>Пробный период {n} дней</t>
+  </si>
+  <si>
+    <t>plan.f.verifiedBadge</t>
+  </si>
+  <si>
+    <t>Verified badge included</t>
+  </si>
+  <si>
+    <t>Галочка верификации включена</t>
+  </si>
+  <si>
+    <t>plan.f.priorityFeed</t>
+  </si>
+  <si>
+    <t>Your cases shown first to attorneys</t>
+  </si>
+  <si>
+    <t>Ваши кейсы — первыми в ленте адвокатов</t>
+  </si>
+  <si>
+    <t>plan.f.maxActiveCases</t>
+  </si>
+  <si>
+    <t>Open cases: up to {n}</t>
+  </si>
+  <si>
+    <t>Открытых кейсов: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedCases</t>
+  </si>
+  <si>
+    <t>Unlimited open cases</t>
+  </si>
+  <si>
+    <t>Открытые кейсы без ограничений</t>
+  </si>
+  <si>
+    <t>plan.seats.extra</t>
+  </si>
+  <si>
+    <t>Extra assistants</t>
+  </si>
+  <si>
+    <t>Доп. помощники</t>
+  </si>
+  <si>
+    <t>plan.seats.each</t>
+  </si>
+  <si>
+    <t>+{price} a month each</t>
+  </si>
+  <si>
+    <t>+{price} в месяц за каждого</t>
+  </si>
+  <si>
+    <t>plan.seats.includedN</t>
+  </si>
+  <si>
+    <t>Included in the plan: {n}</t>
+  </si>
+  <si>
+    <t>Включено в план: {n}</t>
+  </si>
+  <si>
+    <t>plan.seats.limit</t>
+  </si>
+  <si>
+    <t>You can add {n} more</t>
+  </si>
+  <si>
+    <t>Можно добавить ещё: {n}</t>
+  </si>
+  <si>
+    <t>plan.current.title</t>
+  </si>
+  <si>
+    <t>plan.current.includes</t>
+  </si>
+  <si>
+    <t>What's included</t>
+  </si>
+  <si>
+    <t>Что входит</t>
+  </si>
+  <si>
+    <t>plan.seats.summary</t>
+  </si>
+  <si>
+    <t>Assistants: {total} · {included} included, {extra} extra</t>
+  </si>
+  <si>
+    <t>Помощники: {total} · включено {included}, доп. {extra}</t>
+  </si>
+  <si>
+    <t>plan.seats.summary.max</t>
+  </si>
+  <si>
+    <t>Seat limit: {max}</t>
+  </si>
+  <si>
+    <t>Максимум мест: {max}</t>
+  </si>
+  <si>
+    <t>plan.client.title</t>
+  </si>
+  <si>
+    <t>Client subscription</t>
+  </si>
+  <si>
+    <t>Подписка клиента</t>
+  </si>
+  <si>
+    <t>plan.client.hint</t>
+  </si>
+  <si>
+    <t>Badge, priority in the feed, case limits</t>
+  </si>
+  <si>
+    <t>Галочка, приоритет в ленте, лимиты кейсов</t>
+  </si>
+  <si>
+    <t>plan.client.choose</t>
+  </si>
+  <si>
+    <t>Choose a plan</t>
+  </si>
+  <si>
+    <t>Выберите план</t>
+  </si>
+  <si>
+    <t>plan.client.subscribe</t>
+  </si>
+  <si>
+    <t>Subscribe</t>
+  </si>
+  <si>
+    <t>Оформить</t>
+  </si>
+  <si>
+    <t>plan.client.subscribeTrial</t>
+  </si>
+  <si>
+    <t>Subscribe · {n} days free</t>
+  </si>
+  <si>
+    <t>Оформить · {n} дней бесплатно</t>
+  </si>
+  <si>
+    <t>plan.client.cancel</t>
+  </si>
+  <si>
+    <t>Отменить</t>
+  </si>
+  <si>
+    <t>plan.client.resume</t>
+  </si>
+  <si>
+    <t>Resume</t>
+  </si>
+  <si>
+    <t>Возобновить</t>
+  </si>
+  <si>
+    <t>plan.client.trialHint</t>
+  </si>
+  <si>
+    <t>Your first purchase of a plan with a trial is free for the trial days.</t>
+  </si>
+  <si>
+    <t>Первая покупка плана с пробным периодом — бесплатно на время триала.</t>
+  </si>
+  <si>
+    <t>plan.client.line.trialEnds</t>
+  </si>
+  <si>
+    <t>Trial until {date}, then {price}</t>
+  </si>
+  <si>
+    <t>Пробный период до {date}, затем {price}</t>
+  </si>
+  <si>
+    <t>plan.client.line.nextCharge</t>
+  </si>
+  <si>
+    <t>Next charge {date} — {price}</t>
+  </si>
+  <si>
+    <t>Следующее списание {date} — {price}</t>
+  </si>
+  <si>
+    <t>plan.client.line.cancelScheduled</t>
+  </si>
+  <si>
+    <t>Ends on {date}</t>
+  </si>
+  <si>
+    <t>Подписка закончится {date}</t>
+  </si>
+  <si>
+    <t>plan.client.line.pastDue</t>
+  </si>
+  <si>
+    <t>Payment failed — update your card</t>
+  </si>
+  <si>
+    <t>Оплата не прошла — обновите карту</t>
+  </si>
+  <si>
+    <t>plan.client.line.ended</t>
+  </si>
+  <si>
+    <t>Subscription ended</t>
+  </si>
+  <si>
+    <t>Подписка завершена</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.title</t>
+  </si>
+  <si>
+    <t>Cancel the subscription?</t>
+  </si>
+  <si>
+    <t>Отменить подписку?</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.body</t>
+  </si>
+  <si>
+    <t>Access stays until {date}.</t>
+  </si>
+  <si>
+    <t>Доступ сохранится до {date}.</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.bodyNoDate</t>
+  </si>
+  <si>
+    <t>Access stays until the end of the paid period.</t>
+  </si>
+  <si>
+    <t>Доступ сохранится до конца оплаченного периода.</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.done</t>
+  </si>
+  <si>
+    <t>Won't renew</t>
+  </si>
+  <si>
+    <t>Подписка не продлится</t>
+  </si>
+  <si>
+    <t>plan.client.resume.done</t>
+  </si>
+  <si>
+    <t>Subscription resumed</t>
+  </si>
+  <si>
+    <t>Подписка возобновлена</t>
+  </si>
+  <si>
+    <t>plan.client.done.active</t>
+  </si>
+  <si>
+    <t>Subscription active</t>
+  </si>
+  <si>
+    <t>Подписка оформлена</t>
+  </si>
+  <si>
+    <t>plan.client.done.trial</t>
+  </si>
+  <si>
+    <t>Your trial has started</t>
+  </si>
+  <si>
+    <t>Пробный период начался</t>
+  </si>
+  <si>
+    <t>plan.client.noPlans</t>
+  </si>
+  <si>
+    <t>No client plans yet</t>
+  </si>
+  <si>
+    <t>Пока нет планов для клиентов</t>
+  </si>
+  <si>
+    <t>plan.badge.included</t>
+  </si>
+  <si>
+    <t>The badge is included in your plan</t>
+  </si>
+  <si>
+    <t>Галочка включена в ваш план</t>
+  </si>
+  <si>
+    <t>plan.badge.included.hint</t>
+  </si>
+  <si>
+    <t>Once your documents are approved the badge shows — no separate payment.</t>
+  </si>
+  <si>
+    <t>После проверки документов галочка появится без отдельной оплаты.</t>
+  </si>
+  <si>
+    <t>plan.feed.priority</t>
+  </si>
+  <si>
+    <t>PRIORITY</t>
+  </si>
+  <si>
+    <t>ПРИОРИТЕТ</t>
   </si>
 </sst>
 </file>
@@ -6114,7 +6537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C690"/>
+  <dimension ref="A1:C738"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -13711,6 +14134,534 @@
         <v>1908</v>
       </c>
     </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C692" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C693" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C694" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C695" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C696" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C697" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C698" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C699" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C700" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C701" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C702" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C703" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C704" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C705" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C706" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C707" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B708" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C708" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B709" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C709" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C710" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C711" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C712" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B713" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C713" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C714" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C715" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B716" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C716" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B717" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C717" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B718" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C718" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B719" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C719" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B720" t="s">
+        <v>95</v>
+      </c>
+      <c r="C720" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B721" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C721" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B722" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C722" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B723" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C723" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A724" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B724" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C724" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B725" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C725" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B726" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C726" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B727" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C727" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B728" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C728" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B729" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C729" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B730" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C730" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B731" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C731" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B732" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C732" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B733" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C733" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B734" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C734" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A735" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B735" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C735" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A736" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B736" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C736" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A737" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B737" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C737" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A738" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B738" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C738" t="s">
+        <v>2049</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="2050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="2074">
   <si>
     <t>key</t>
   </si>
@@ -5821,24 +5821,6 @@
     <t>Приоритет в поиске</t>
   </si>
   <si>
-    <t>plan.f.videoCalls</t>
-  </si>
-  <si>
-    <t>Video calls</t>
-  </si>
-  <si>
-    <t>Видеозвонки</t>
-  </si>
-  <si>
-    <t>plan.f.documentTemplates</t>
-  </si>
-  <si>
-    <t>Document templates</t>
-  </si>
-  <si>
-    <t>Шаблоны документов</t>
-  </si>
-  <si>
     <t>plan.f.trial</t>
   </si>
   <si>
@@ -6161,6 +6143,96 @@
   </si>
   <si>
     <t>ПРИОРИТЕТ</t>
+  </si>
+  <si>
+    <t>plan.f.calls</t>
+  </si>
+  <si>
+    <t>In-app calls</t>
+  </si>
+  <si>
+    <t>Звонки в приложении</t>
+  </si>
+  <si>
+    <t>plan.f.chatTranslate</t>
+  </si>
+  <si>
+    <t>Chat translation</t>
+  </si>
+  <si>
+    <t>Перевод сообщений в чате</t>
+  </si>
+  <si>
+    <t>plan.f.translationsPerDay</t>
+  </si>
+  <si>
+    <t>Translations per day: up to {n}</t>
+  </si>
+  <si>
+    <t>Переводов в день: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedTranslations</t>
+  </si>
+  <si>
+    <t>Unlimited translations</t>
+  </si>
+  <si>
+    <t>Переводы без ограничений</t>
+  </si>
+  <si>
+    <t>plan.f.videoPosts</t>
+  </si>
+  <si>
+    <t>Video posts (reels)</t>
+  </si>
+  <si>
+    <t>Видеопосты (рилсы)</t>
+  </si>
+  <si>
+    <t>plan.f.postsPerDay</t>
+  </si>
+  <si>
+    <t>Posts per day: up to {n}</t>
+  </si>
+  <si>
+    <t>Постов в день: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedPosts</t>
+  </si>
+  <si>
+    <t>No daily post limit</t>
+  </si>
+  <si>
+    <t>Посты без дневного лимита</t>
+  </si>
+  <si>
+    <t>plan.f.videosPerDay</t>
+  </si>
+  <si>
+    <t>Videos per day: up to {n}</t>
+  </si>
+  <si>
+    <t>Видео в день: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedVideos</t>
+  </si>
+  <si>
+    <t>No daily video limit</t>
+  </si>
+  <si>
+    <t>Видео без дневного лимита</t>
+  </si>
+  <si>
+    <t>plan.f.casePromotion</t>
+  </si>
+  <si>
+    <t>Case promotion</t>
+  </si>
+  <si>
+    <t>Продвижение кейсов</t>
   </si>
 </sst>
 </file>
@@ -6537,7 +6609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C738"/>
+  <dimension ref="A1:C746"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -14337,32 +14409,32 @@
         <v>1963</v>
       </c>
       <c r="B709" t="s">
-        <v>1964</v>
+        <v>1913</v>
       </c>
       <c r="C709" t="s">
-        <v>1965</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C710" t="s">
         <v>1966</v>
-      </c>
-      <c r="B710" t="s">
-        <v>1967</v>
-      </c>
-      <c r="C710" t="s">
-        <v>1968</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C711" t="s">
         <v>1969</v>
-      </c>
-      <c r="B711" t="s">
-        <v>1913</v>
-      </c>
-      <c r="C711" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
@@ -14436,29 +14508,29 @@
         <v>1988</v>
       </c>
       <c r="B718" t="s">
+        <v>95</v>
+      </c>
+      <c r="C718" t="s">
         <v>1989</v>
-      </c>
-      <c r="C718" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B719" t="s">
         <v>1991</v>
       </c>
-      <c r="B719" t="s">
+      <c r="C719" t="s">
         <v>1992</v>
-      </c>
-      <c r="C719" t="s">
-        <v>1993</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B720" t="s">
         <v>1994</v>
-      </c>
-      <c r="B720" t="s">
-        <v>95</v>
       </c>
       <c r="C720" t="s">
         <v>1995</v>
@@ -14660,6 +14732,94 @@
       </c>
       <c r="C738" t="s">
         <v>2049</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A739" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B739" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C739" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A740" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B740" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C740" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A741" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B741" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C741" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A742" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B742" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C742" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A743" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B743" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C743" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A744" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B744" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C744" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A745" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B745" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C745" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A746" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B746" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C746" t="s">
+        <v>2073</v>
       </c>
     </row>
   </sheetData>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="2074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="2086">
   <si>
     <t>key</t>
   </si>
@@ -6233,6 +6233,42 @@
   </si>
   <si>
     <t>Продвижение кейсов</t>
+  </si>
+  <si>
+    <t>error.api.ENTITLEMENT_REQUIRED</t>
+  </si>
+  <si>
+    <t>This feature is not part of your plan.</t>
+  </si>
+  <si>
+    <t>Эта возможность не входит в ваш план.</t>
+  </si>
+  <si>
+    <t>error.api.BID_LIMIT_REACHED</t>
+  </si>
+  <si>
+    <t>You've reached your plan's limit of active offers.</t>
+  </si>
+  <si>
+    <t>Достигнут лимит активных ставок вашего плана.</t>
+  </si>
+  <si>
+    <t>error.api.CASE_LIMIT_REACHED</t>
+  </si>
+  <si>
+    <t>You've reached your plan's limit of open cases.</t>
+  </si>
+  <si>
+    <t>Достигнут лимит открытых кейсов вашего плана.</t>
+  </si>
+  <si>
+    <t>error.api.PLAN_NOT_AVAILABLE</t>
+  </si>
+  <si>
+    <t>This plan is not available right now. Refresh the screen.</t>
+  </si>
+  <si>
+    <t>Этот план сейчас недоступен. Обновите экран.</t>
   </si>
 </sst>
 </file>
@@ -6609,7 +6645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C746"/>
+  <dimension ref="A1:C750"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -14822,6 +14858,50 @@
         <v>2073</v>
       </c>
     </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A747" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B747" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C747" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A748" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B748" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C748" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A749" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B749" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C749" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A750" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B750" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C750" t="s">
+        <v>2085</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="1909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="2089">
   <si>
     <t>key</t>
   </si>
@@ -5738,6 +5738,546 @@
   </si>
   <si>
     <t>Выбрать практики</t>
+  </si>
+  <si>
+    <t>plan.free</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Бесплатно</t>
+  </si>
+  <si>
+    <t>plan.status.yours</t>
+  </si>
+  <si>
+    <t>Your plan</t>
+  </si>
+  <si>
+    <t>Ваш план</t>
+  </si>
+  <si>
+    <t>plan.pay.trialDays</t>
+  </si>
+  <si>
+    <t>Start {n} days free</t>
+  </si>
+  <si>
+    <t>Начать {n} дней бесплатно</t>
+  </si>
+  <si>
+    <t>plan.f.seatsIncluded</t>
+  </si>
+  <si>
+    <t>Assistants included: {n}</t>
+  </si>
+  <si>
+    <t>Помощников включено: {n}</t>
+  </si>
+  <si>
+    <t>plan.f.extraSeat</t>
+  </si>
+  <si>
+    <t>Extra assistant: {price}/mo</t>
+  </si>
+  <si>
+    <t>Доп. помощник: {price}/мес</t>
+  </si>
+  <si>
+    <t>plan.f.bidsAnyState</t>
+  </si>
+  <si>
+    <t>Offers in any state</t>
+  </si>
+  <si>
+    <t>Ставки в любом штате</t>
+  </si>
+  <si>
+    <t>plan.f.maxActiveBids</t>
+  </si>
+  <si>
+    <t>Active offers: up to {n}</t>
+  </si>
+  <si>
+    <t>Активных ставок: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedBids</t>
+  </si>
+  <si>
+    <t>Unlimited active offers</t>
+  </si>
+  <si>
+    <t>Активные ставки без ограничений</t>
+  </si>
+  <si>
+    <t>plan.f.prioritySearch</t>
+  </si>
+  <si>
+    <t>Higher in search</t>
+  </si>
+  <si>
+    <t>Приоритет в поиске</t>
+  </si>
+  <si>
+    <t>plan.f.trial</t>
+  </si>
+  <si>
+    <t>{n}-day free trial</t>
+  </si>
+  <si>
+    <t>Пробный период {n} дней</t>
+  </si>
+  <si>
+    <t>plan.f.verifiedBadge</t>
+  </si>
+  <si>
+    <t>Verified badge included</t>
+  </si>
+  <si>
+    <t>Галочка верификации включена</t>
+  </si>
+  <si>
+    <t>plan.f.priorityFeed</t>
+  </si>
+  <si>
+    <t>Your cases shown first to attorneys</t>
+  </si>
+  <si>
+    <t>Ваши кейсы — первыми в ленте адвокатов</t>
+  </si>
+  <si>
+    <t>plan.f.maxActiveCases</t>
+  </si>
+  <si>
+    <t>Open cases: up to {n}</t>
+  </si>
+  <si>
+    <t>Открытых кейсов: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedCases</t>
+  </si>
+  <si>
+    <t>Unlimited open cases</t>
+  </si>
+  <si>
+    <t>Открытые кейсы без ограничений</t>
+  </si>
+  <si>
+    <t>plan.seats.extra</t>
+  </si>
+  <si>
+    <t>Extra assistants</t>
+  </si>
+  <si>
+    <t>Доп. помощники</t>
+  </si>
+  <si>
+    <t>plan.seats.each</t>
+  </si>
+  <si>
+    <t>+{price} a month each</t>
+  </si>
+  <si>
+    <t>+{price} в месяц за каждого</t>
+  </si>
+  <si>
+    <t>plan.seats.includedN</t>
+  </si>
+  <si>
+    <t>Included in the plan: {n}</t>
+  </si>
+  <si>
+    <t>Включено в план: {n}</t>
+  </si>
+  <si>
+    <t>plan.seats.limit</t>
+  </si>
+  <si>
+    <t>You can add {n} more</t>
+  </si>
+  <si>
+    <t>Можно добавить ещё: {n}</t>
+  </si>
+  <si>
+    <t>plan.current.title</t>
+  </si>
+  <si>
+    <t>plan.current.includes</t>
+  </si>
+  <si>
+    <t>What's included</t>
+  </si>
+  <si>
+    <t>Что входит</t>
+  </si>
+  <si>
+    <t>plan.seats.summary</t>
+  </si>
+  <si>
+    <t>Assistants: {total} · {included} included, {extra} extra</t>
+  </si>
+  <si>
+    <t>Помощники: {total} · включено {included}, доп. {extra}</t>
+  </si>
+  <si>
+    <t>plan.seats.summary.max</t>
+  </si>
+  <si>
+    <t>Seat limit: {max}</t>
+  </si>
+  <si>
+    <t>Максимум мест: {max}</t>
+  </si>
+  <si>
+    <t>plan.client.title</t>
+  </si>
+  <si>
+    <t>Client subscription</t>
+  </si>
+  <si>
+    <t>Подписка клиента</t>
+  </si>
+  <si>
+    <t>plan.client.hint</t>
+  </si>
+  <si>
+    <t>Badge, priority in the feed, case limits</t>
+  </si>
+  <si>
+    <t>Галочка, приоритет в ленте, лимиты кейсов</t>
+  </si>
+  <si>
+    <t>plan.client.choose</t>
+  </si>
+  <si>
+    <t>Choose a plan</t>
+  </si>
+  <si>
+    <t>Выберите план</t>
+  </si>
+  <si>
+    <t>plan.client.subscribe</t>
+  </si>
+  <si>
+    <t>Subscribe</t>
+  </si>
+  <si>
+    <t>Оформить</t>
+  </si>
+  <si>
+    <t>plan.client.subscribeTrial</t>
+  </si>
+  <si>
+    <t>Subscribe · {n} days free</t>
+  </si>
+  <si>
+    <t>Оформить · {n} дней бесплатно</t>
+  </si>
+  <si>
+    <t>plan.client.cancel</t>
+  </si>
+  <si>
+    <t>Отменить</t>
+  </si>
+  <si>
+    <t>plan.client.resume</t>
+  </si>
+  <si>
+    <t>Resume</t>
+  </si>
+  <si>
+    <t>Возобновить</t>
+  </si>
+  <si>
+    <t>plan.client.trialHint</t>
+  </si>
+  <si>
+    <t>Your first purchase of a plan with a trial is free for the trial days.</t>
+  </si>
+  <si>
+    <t>Первая покупка плана с пробным периодом — бесплатно на время триала.</t>
+  </si>
+  <si>
+    <t>plan.client.line.trialEnds</t>
+  </si>
+  <si>
+    <t>Trial until {date}, then {price}</t>
+  </si>
+  <si>
+    <t>Пробный период до {date}, затем {price}</t>
+  </si>
+  <si>
+    <t>plan.client.line.nextCharge</t>
+  </si>
+  <si>
+    <t>Next charge {date} — {price}</t>
+  </si>
+  <si>
+    <t>Следующее списание {date} — {price}</t>
+  </si>
+  <si>
+    <t>plan.client.line.cancelScheduled</t>
+  </si>
+  <si>
+    <t>Ends on {date}</t>
+  </si>
+  <si>
+    <t>Подписка закончится {date}</t>
+  </si>
+  <si>
+    <t>plan.client.line.pastDue</t>
+  </si>
+  <si>
+    <t>Payment failed — update your card</t>
+  </si>
+  <si>
+    <t>Оплата не прошла — обновите карту</t>
+  </si>
+  <si>
+    <t>plan.client.line.ended</t>
+  </si>
+  <si>
+    <t>Subscription ended</t>
+  </si>
+  <si>
+    <t>Подписка завершена</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.title</t>
+  </si>
+  <si>
+    <t>Cancel the subscription?</t>
+  </si>
+  <si>
+    <t>Отменить подписку?</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.body</t>
+  </si>
+  <si>
+    <t>Access stays until {date}.</t>
+  </si>
+  <si>
+    <t>Доступ сохранится до {date}.</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.bodyNoDate</t>
+  </si>
+  <si>
+    <t>Access stays until the end of the paid period.</t>
+  </si>
+  <si>
+    <t>Доступ сохранится до конца оплаченного периода.</t>
+  </si>
+  <si>
+    <t>plan.client.cancel.done</t>
+  </si>
+  <si>
+    <t>Won't renew</t>
+  </si>
+  <si>
+    <t>Подписка не продлится</t>
+  </si>
+  <si>
+    <t>plan.client.resume.done</t>
+  </si>
+  <si>
+    <t>Subscription resumed</t>
+  </si>
+  <si>
+    <t>Подписка возобновлена</t>
+  </si>
+  <si>
+    <t>plan.client.done.active</t>
+  </si>
+  <si>
+    <t>Subscription active</t>
+  </si>
+  <si>
+    <t>Подписка оформлена</t>
+  </si>
+  <si>
+    <t>plan.client.done.trial</t>
+  </si>
+  <si>
+    <t>Your trial has started</t>
+  </si>
+  <si>
+    <t>Пробный период начался</t>
+  </si>
+  <si>
+    <t>plan.client.noPlans</t>
+  </si>
+  <si>
+    <t>No client plans yet</t>
+  </si>
+  <si>
+    <t>Пока нет планов для клиентов</t>
+  </si>
+  <si>
+    <t>plan.badge.included</t>
+  </si>
+  <si>
+    <t>The badge is included in your plan</t>
+  </si>
+  <si>
+    <t>Галочка включена в ваш план</t>
+  </si>
+  <si>
+    <t>plan.badge.included.hint</t>
+  </si>
+  <si>
+    <t>Once your documents are approved the badge shows — no separate payment.</t>
+  </si>
+  <si>
+    <t>После проверки документов галочка появится без отдельной оплаты.</t>
+  </si>
+  <si>
+    <t>plan.feed.priority</t>
+  </si>
+  <si>
+    <t>PRIORITY</t>
+  </si>
+  <si>
+    <t>ПРИОРИТЕТ</t>
+  </si>
+  <si>
+    <t>plan.f.calls</t>
+  </si>
+  <si>
+    <t>In-app calls</t>
+  </si>
+  <si>
+    <t>Звонки в приложении</t>
+  </si>
+  <si>
+    <t>plan.f.videoCalls</t>
+  </si>
+  <si>
+    <t>Video calls</t>
+  </si>
+  <si>
+    <t>Видеозвонки</t>
+  </si>
+  <si>
+    <t>plan.f.chatTranslate</t>
+  </si>
+  <si>
+    <t>Chat translation</t>
+  </si>
+  <si>
+    <t>Перевод сообщений в чате</t>
+  </si>
+  <si>
+    <t>plan.f.translationsPerDay</t>
+  </si>
+  <si>
+    <t>Translations per day: up to {n}</t>
+  </si>
+  <si>
+    <t>Переводов в день: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedTranslations</t>
+  </si>
+  <si>
+    <t>Unlimited translations</t>
+  </si>
+  <si>
+    <t>Переводы без ограничений</t>
+  </si>
+  <si>
+    <t>plan.f.videoPosts</t>
+  </si>
+  <si>
+    <t>Video posts (reels)</t>
+  </si>
+  <si>
+    <t>Видеопосты (рилсы)</t>
+  </si>
+  <si>
+    <t>plan.f.postsPerDay</t>
+  </si>
+  <si>
+    <t>Posts per day: up to {n}</t>
+  </si>
+  <si>
+    <t>Постов в день: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedPosts</t>
+  </si>
+  <si>
+    <t>No daily post limit</t>
+  </si>
+  <si>
+    <t>Посты без дневного лимита</t>
+  </si>
+  <si>
+    <t>plan.f.videosPerDay</t>
+  </si>
+  <si>
+    <t>Videos per day: up to {n}</t>
+  </si>
+  <si>
+    <t>Видео в день: до {n}</t>
+  </si>
+  <si>
+    <t>plan.f.unlimitedVideos</t>
+  </si>
+  <si>
+    <t>No daily video limit</t>
+  </si>
+  <si>
+    <t>Видео без дневного лимита</t>
+  </si>
+  <si>
+    <t>plan.f.casePromotion</t>
+  </si>
+  <si>
+    <t>Case promotion</t>
+  </si>
+  <si>
+    <t>Продвижение кейсов</t>
+  </si>
+  <si>
+    <t>error.api.ENTITLEMENT_REQUIRED</t>
+  </si>
+  <si>
+    <t>This feature is not part of your plan.</t>
+  </si>
+  <si>
+    <t>Эта возможность не входит в ваш план.</t>
+  </si>
+  <si>
+    <t>error.api.BID_LIMIT_REACHED</t>
+  </si>
+  <si>
+    <t>You've reached your plan's limit of active offers.</t>
+  </si>
+  <si>
+    <t>Достигнут лимит активных ставок вашего плана.</t>
+  </si>
+  <si>
+    <t>error.api.CASE_LIMIT_REACHED</t>
+  </si>
+  <si>
+    <t>You've reached your plan's limit of open cases.</t>
+  </si>
+  <si>
+    <t>Достигнут лимит открытых кейсов вашего плана.</t>
+  </si>
+  <si>
+    <t>error.api.PLAN_NOT_AVAILABLE</t>
+  </si>
+  <si>
+    <t>This plan is not available right now. Refresh the screen.</t>
+  </si>
+  <si>
+    <t>Этот план сейчас недоступен. Обновите экран.</t>
   </si>
 </sst>
 </file>
@@ -6114,7 +6654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C690"/>
+  <dimension ref="A1:C751"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -13711,6 +14251,677 @@
         <v>1908</v>
       </c>
     </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C692" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C693" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C694" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C695" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C696" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C697" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C698" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C699" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C700" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C701" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C702" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C703" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C704" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C705" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C706" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C707" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B708" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C708" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B709" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C709" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C710" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C711" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C712" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B713" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C713" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C714" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C715" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B716" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C716" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B717" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C717" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B718" t="s">
+        <v>95</v>
+      </c>
+      <c r="C718" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B719" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C719" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B720" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C720" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B721" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C721" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B722" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C722" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B723" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C723" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A724" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B724" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C724" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B725" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C725" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B726" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C726" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B727" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C727" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B728" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C728" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B729" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C729" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B730" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C730" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B731" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C731" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B732" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C732" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B733" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C733" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B734" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C734" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A735" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B735" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C735" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A736" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B736" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C736" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A737" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B737" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C737" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A738" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B738" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C738" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A739" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B739" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C739" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A740" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B740" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C740" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A741" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B741" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C741" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A742" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B742" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C742" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A743" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B743" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C743" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A744" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B744" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C744" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A745" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B745" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C745" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A746" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B746" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C746" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A747" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B747" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C747" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A748" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B748" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C748" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A749" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B749" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C749" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A750" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B750" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C750" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A751" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B751" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C751" t="s">
+        <v>2088</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/api/prisma/seed/translations_seed.xlsx
+++ b/apps/api/prisma/seed/translations_seed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="2511">
   <si>
     <t>key</t>
   </si>
@@ -6278,6 +6278,1272 @@
   </si>
   <si>
     <t>Этот план сейчас недоступен. Обновите экран.</t>
+  </si>
+  <si>
+    <t>cases.facts.deadline</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>Срок</t>
+  </si>
+  <si>
+    <t>cases.card.locked</t>
+  </si>
+  <si>
+    <t>locked</t>
+  </si>
+  <si>
+    <t>закрыто</t>
+  </si>
+  <si>
+    <t>cases.card.bid</t>
+  </si>
+  <si>
+    <t>Бид</t>
+  </si>
+  <si>
+    <t>cases.work.chatWithClient</t>
+  </si>
+  <si>
+    <t>Chat with client</t>
+  </si>
+  <si>
+    <t>Чат с клиентом</t>
+  </si>
+  <si>
+    <t>cases.owner.chatWithLawyer</t>
+  </si>
+  <si>
+    <t>Chat with lawyer</t>
+  </si>
+  <si>
+    <t>Чат с юристом</t>
+  </si>
+  <si>
+    <t>cases.status.acceptedByBoth</t>
+  </si>
+  <si>
+    <t>Accepted by both</t>
+  </si>
+  <si>
+    <t>Принят обеими сторонами</t>
+  </si>
+  <si>
+    <t>cases.tab.overview</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Обзор</t>
+  </si>
+  <si>
+    <t>cases.tab.files</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>Файлы</t>
+  </si>
+  <si>
+    <t>cases.tab.tasks</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Задачи</t>
+  </si>
+  <si>
+    <t>cases.tab.updates</t>
+  </si>
+  <si>
+    <t>Updates</t>
+  </si>
+  <si>
+    <t>Обновления</t>
+  </si>
+  <si>
+    <t>cases.tab.activity</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Активность</t>
+  </si>
+  <si>
+    <t>cases.detail.where</t>
+  </si>
+  <si>
+    <t>Where</t>
+  </si>
+  <si>
+    <t>Где</t>
+  </si>
+  <si>
+    <t>cases.files.documents</t>
+  </si>
+  <si>
+    <t>cases.files.photos</t>
+  </si>
+  <si>
+    <t>Photos</t>
+  </si>
+  <si>
+    <t>Фото</t>
+  </si>
+  <si>
+    <t>cases.files.all</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Все</t>
+  </si>
+  <si>
+    <t>cases.files.fromTasks</t>
+  </si>
+  <si>
+    <t>From tasks</t>
+  </si>
+  <si>
+    <t>Из задач</t>
+  </si>
+  <si>
+    <t>cases.files.fromUpdates</t>
+  </si>
+  <si>
+    <t>From updates</t>
+  </si>
+  <si>
+    <t>Из обновлений</t>
+  </si>
+  <si>
+    <t>cases.files.samples</t>
+  </si>
+  <si>
+    <t>Samples</t>
+  </si>
+  <si>
+    <t>Образцы</t>
+  </si>
+  <si>
+    <t>cases.files.empty</t>
+  </si>
+  <si>
+    <t>No files yet</t>
+  </si>
+  <si>
+    <t>Файлов пока нет</t>
+  </si>
+  <si>
+    <t>cases.files.photo</t>
+  </si>
+  <si>
+    <t>Photo</t>
+  </si>
+  <si>
+    <t>cases.files.sample</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>Образец</t>
+  </si>
+  <si>
+    <t>cases.files.fromLawyer</t>
+  </si>
+  <si>
+    <t>From lawyer</t>
+  </si>
+  <si>
+    <t>От юриста</t>
+  </si>
+  <si>
+    <t>cases.files.fromTask</t>
+  </si>
+  <si>
+    <t>From task: {title}</t>
+  </si>
+  <si>
+    <t>Из задачи: {title}</t>
+  </si>
+  <si>
+    <t>cases.files.fromUpdate</t>
+  </si>
+  <si>
+    <t>From update</t>
+  </si>
+  <si>
+    <t>Из обновления</t>
+  </si>
+  <si>
+    <t>cases.files.download</t>
+  </si>
+  <si>
+    <t>Download</t>
+  </si>
+  <si>
+    <t>Скачать</t>
+  </si>
+  <si>
+    <t>cases.files.openBtn</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Открыть</t>
+  </si>
+  <si>
+    <t>cases.files.count.one</t>
+  </si>
+  <si>
+    <t>{count} file</t>
+  </si>
+  <si>
+    <t>{count} файл</t>
+  </si>
+  <si>
+    <t>cases.files.count.other</t>
+  </si>
+  <si>
+    <t>{count} files</t>
+  </si>
+  <si>
+    <t>{count} файла</t>
+  </si>
+  <si>
+    <t>cases.role.client</t>
+  </si>
+  <si>
+    <t>cases.role.attorney</t>
+  </si>
+  <si>
+    <t>Licensed Attorney</t>
+  </si>
+  <si>
+    <t>Юрист с лицензией</t>
+  </si>
+  <si>
+    <t>cases.updates.write</t>
+  </si>
+  <si>
+    <t>Write an update…</t>
+  </si>
+  <si>
+    <t>Напишите обновление…</t>
+  </si>
+  <si>
+    <t>cases.updates.me</t>
+  </si>
+  <si>
+    <t>Me</t>
+  </si>
+  <si>
+    <t>Я</t>
+  </si>
+  <si>
+    <t>cases.updates.empty</t>
+  </si>
+  <si>
+    <t>No updates yet</t>
+  </si>
+  <si>
+    <t>Обновлений пока нет</t>
+  </si>
+  <si>
+    <t>cases.updates.taskDone</t>
+  </si>
+  <si>
+    <t>Done: {title}</t>
+  </si>
+  <si>
+    <t>Выполнено: {title}</t>
+  </si>
+  <si>
+    <t>cases.updates.taskFiles</t>
+  </si>
+  <si>
+    <t>Added to the task: {title}</t>
+  </si>
+  <si>
+    <t>Добавлено в задачу: {title}</t>
+  </si>
+  <si>
+    <t>cases.activity.empty</t>
+  </si>
+  <si>
+    <t>Nothing has happened yet</t>
+  </si>
+  <si>
+    <t>Пока ничего не происходило</t>
+  </si>
+  <si>
+    <t>cases.activity.update</t>
+  </si>
+  <si>
+    <t>{name} wrote an update</t>
+  </si>
+  <si>
+    <t>{name} написал(а) обновление</t>
+  </si>
+  <si>
+    <t>cases.activity.taskCreated</t>
+  </si>
+  <si>
+    <t>{name} created the task “{title}”</t>
+  </si>
+  <si>
+    <t>{name} создал(а) задачу «{title}»</t>
+  </si>
+  <si>
+    <t>cases.activity.taskDone</t>
+  </si>
+  <si>
+    <t>{name} completed “{title}”</t>
+  </si>
+  <si>
+    <t>{name} выполнил(а) «{title}»</t>
+  </si>
+  <si>
+    <t>cases.activity.taskUndone</t>
+  </si>
+  <si>
+    <t>{name} unmarked “{title}”</t>
+  </si>
+  <si>
+    <t>{name} снял(а) отметку «{title}»</t>
+  </si>
+  <si>
+    <t>cases.activity.taskClosed</t>
+  </si>
+  <si>
+    <t>{name} closed “{title}”</t>
+  </si>
+  <si>
+    <t>{name} закрыл(а) «{title}»</t>
+  </si>
+  <si>
+    <t>cases.activity.taskReopened</t>
+  </si>
+  <si>
+    <t>{name} reopened “{title}”</t>
+  </si>
+  <si>
+    <t>{name} открыл(а) заново «{title}»</t>
+  </si>
+  <si>
+    <t>cases.activity.filesAdded</t>
+  </si>
+  <si>
+    <t>{name} added {count} files to “{title}”</t>
+  </si>
+  <si>
+    <t>{name} добавил(а) в «{title}» файлы: {count}</t>
+  </si>
+  <si>
+    <t>cases.tasks.forClient</t>
+  </si>
+  <si>
+    <t>For client</t>
+  </si>
+  <si>
+    <t>Для клиента</t>
+  </si>
+  <si>
+    <t>cases.tasks.shared</t>
+  </si>
+  <si>
+    <t>Shared</t>
+  </si>
+  <si>
+    <t>Общие</t>
+  </si>
+  <si>
+    <t>cases.tasks.private</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>Личные</t>
+  </si>
+  <si>
+    <t>cases.tasks.yours</t>
+  </si>
+  <si>
+    <t>Your tasks</t>
+  </si>
+  <si>
+    <t>Ваши задачи</t>
+  </si>
+  <si>
+    <t>cases.tasks.lawyerProgress</t>
+  </si>
+  <si>
+    <t>Lawyer's progress</t>
+  </si>
+  <si>
+    <t>Работа юриста</t>
+  </si>
+  <si>
+    <t>cases.tasks.forClientHint</t>
+  </si>
+  <si>
+    <t>The client sees it, answers and attaches files</t>
+  </si>
+  <si>
+    <t>Клиент видит, отвечает и прикладывает файлы</t>
+  </si>
+  <si>
+    <t>cases.tasks.sharedHint</t>
+  </si>
+  <si>
+    <t>The client sees it, only you tick it</t>
+  </si>
+  <si>
+    <t>Клиент видит, отмечаете только вы</t>
+  </si>
+  <si>
+    <t>cases.tasks.privateHint</t>
+  </si>
+  <si>
+    <t>Only for you, the client does not see it</t>
+  </si>
+  <si>
+    <t>Только для вас, клиент не видит</t>
+  </si>
+  <si>
+    <t>cases.tasks.add</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Задача</t>
+  </si>
+  <si>
+    <t>cases.tasks.empty</t>
+  </si>
+  <si>
+    <t>cases.tasks.toDo</t>
+  </si>
+  <si>
+    <t>To do</t>
+  </si>
+  <si>
+    <t>Нужно сделать</t>
+  </si>
+  <si>
+    <t>cases.tasks.waitingClient</t>
+  </si>
+  <si>
+    <t>Waiting for the client</t>
+  </si>
+  <si>
+    <t>Ждём клиента</t>
+  </si>
+  <si>
+    <t>cases.tasks.doneOn</t>
+  </si>
+  <si>
+    <t>Done {date}</t>
+  </si>
+  <si>
+    <t>Выполнено {date}</t>
+  </si>
+  <si>
+    <t>cases.tasks.closedOn</t>
+  </si>
+  <si>
+    <t>Closed {date}</t>
+  </si>
+  <si>
+    <t>Закрыто {date}</t>
+  </si>
+  <si>
+    <t>cases.tasks.progress</t>
+  </si>
+  <si>
+    <t>{done} of {total}</t>
+  </si>
+  <si>
+    <t>{done} из {total}</t>
+  </si>
+  <si>
+    <t>cases.tasks.addFile</t>
+  </si>
+  <si>
+    <t>Add file</t>
+  </si>
+  <si>
+    <t>Добавить файл</t>
+  </si>
+  <si>
+    <t>cases.tasks.addFiles</t>
+  </si>
+  <si>
+    <t>Add files</t>
+  </si>
+  <si>
+    <t>Добавить файлы</t>
+  </si>
+  <si>
+    <t>cases.tasks.addMore</t>
+  </si>
+  <si>
+    <t>Add more</t>
+  </si>
+  <si>
+    <t>Добавить ещё</t>
+  </si>
+  <si>
+    <t>cases.tasks.done</t>
+  </si>
+  <si>
+    <t>cases.tasks.markDone</t>
+  </si>
+  <si>
+    <t>Mark done</t>
+  </si>
+  <si>
+    <t>Отметить выполненной</t>
+  </si>
+  <si>
+    <t>cases.tasks.undo</t>
+  </si>
+  <si>
+    <t>Unmark</t>
+  </si>
+  <si>
+    <t>Снять отметку</t>
+  </si>
+  <si>
+    <t>cases.tasks.close</t>
+  </si>
+  <si>
+    <t>cases.tasks.reopen</t>
+  </si>
+  <si>
+    <t>Reopen</t>
+  </si>
+  <si>
+    <t>Открыть заново</t>
+  </si>
+  <si>
+    <t>cases.compose.newTask</t>
+  </si>
+  <si>
+    <t>New task</t>
+  </si>
+  <si>
+    <t>Новая задача</t>
+  </si>
+  <si>
+    <t>cases.compose.newUpdate</t>
+  </si>
+  <si>
+    <t>New update</t>
+  </si>
+  <si>
+    <t>Новое обновление</t>
+  </si>
+  <si>
+    <t>cases.compose.addFiles</t>
+  </si>
+  <si>
+    <t>cases.compose.create</t>
+  </si>
+  <si>
+    <t>cases.compose.send</t>
+  </si>
+  <si>
+    <t>Send</t>
+  </si>
+  <si>
+    <t>Отправить</t>
+  </si>
+  <si>
+    <t>cases.compose.titleHint</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>cases.compose.taskHint</t>
+  </si>
+  <si>
+    <t>Describe the task</t>
+  </si>
+  <si>
+    <t>Описание задачи</t>
+  </si>
+  <si>
+    <t>cases.compose.updateHint</t>
+  </si>
+  <si>
+    <t>What's new in the case?</t>
+  </si>
+  <si>
+    <t>Что нового по кейсу?</t>
+  </si>
+  <si>
+    <t>cases.compose.noteHint</t>
+  </si>
+  <si>
+    <t>Note (optional)</t>
+  </si>
+  <si>
+    <t>Заметка (необязательно)</t>
+  </si>
+  <si>
+    <t>cases.compose.fileNoteHint</t>
+  </si>
+  <si>
+    <t>What's in this file</t>
+  </si>
+  <si>
+    <t>Что на этом файле</t>
+  </si>
+  <si>
+    <t>cases.compose.checklist</t>
+  </si>
+  <si>
+    <t>Checklist item</t>
+  </si>
+  <si>
+    <t>Пункт списка</t>
+  </si>
+  <si>
+    <t>cases.compose.due</t>
+  </si>
+  <si>
+    <t>Due date</t>
+  </si>
+  <si>
+    <t>mine.tab.activeCases</t>
+  </si>
+  <si>
+    <t>Active cases</t>
+  </si>
+  <si>
+    <t>Активные дела</t>
+  </si>
+  <si>
+    <t>cases.tasks.dueOn</t>
+  </si>
+  <si>
+    <t>due {date}</t>
+  </si>
+  <si>
+    <t>cases.compose.remind</t>
+  </si>
+  <si>
+    <t>Reminder</t>
+  </si>
+  <si>
+    <t>Напоминание</t>
+  </si>
+  <si>
+    <t>cases.compose.attach</t>
+  </si>
+  <si>
+    <t>Attach</t>
+  </si>
+  <si>
+    <t>Прикрепить</t>
+  </si>
+  <si>
+    <t>cases.compose.photo</t>
+  </si>
+  <si>
+    <t>cases.compose.file</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Файл</t>
+  </si>
+  <si>
+    <t>cases.compose.samplePhoto</t>
+  </si>
+  <si>
+    <t>Sample (photo)</t>
+  </si>
+  <si>
+    <t>Образец (фото)</t>
+  </si>
+  <si>
+    <t>cases.compose.sampleFile</t>
+  </si>
+  <si>
+    <t>Sample (file)</t>
+  </si>
+  <si>
+    <t>Образец (файл)</t>
+  </si>
+  <si>
+    <t>caseInvites.cancel</t>
+  </si>
+  <si>
+    <t>caseInvites.cancel.confirm</t>
+  </si>
+  <si>
+    <t>Cancel this invite?</t>
+  </si>
+  <si>
+    <t>Отменить приглашение?</t>
+  </si>
+  <si>
+    <t>caseInvites.cancelled</t>
+  </si>
+  <si>
+    <t>Invite cancelled</t>
+  </si>
+  <si>
+    <t>Приглашение отменено</t>
+  </si>
+  <si>
+    <t>caseInvites.reason</t>
+  </si>
+  <si>
+    <t>Reason: {reason}</t>
+  </si>
+  <si>
+    <t>Причина: {reason}</t>
+  </si>
+  <si>
+    <t>caseInvites.title</t>
+  </si>
+  <si>
+    <t>Invited attorneys</t>
+  </si>
+  <si>
+    <t>Приглашённые адвокаты</t>
+  </si>
+  <si>
+    <t>cases.accept.mismatchIntro</t>
+  </si>
+  <si>
+    <t>Please note:</t>
+  </si>
+  <si>
+    <t>Обратите внимание:</t>
+  </si>
+  <si>
+    <t>cases.accept.unverifiedLine</t>
+  </si>
+  <si>
+    <t>The attorney's license is not checked by LawBid — verify it with the state bar.</t>
+  </si>
+  <si>
+    <t>Лицензия адвоката не проверена LawBid — проверьте её в коллегии штата.</t>
+  </si>
+  <si>
+    <t>cases.contacts.notShared</t>
+  </si>
+  <si>
+    <t>The client's contacts are not available yet. Reopen the screen or contact support.</t>
+  </si>
+  <si>
+    <t>Контакты клиента пока не доступны. Откройте экран заново или обратитесь в поддержку.</t>
+  </si>
+  <si>
+    <t>cases.cover.auto</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Авто</t>
+  </si>
+  <si>
+    <t>cases.cover.covers</t>
+  </si>
+  <si>
+    <t>Covers</t>
+  </si>
+  <si>
+    <t>Обложки</t>
+  </si>
+  <si>
+    <t>cases.cover.iconOption</t>
+  </si>
+  <si>
+    <t>Icon {n}</t>
+  </si>
+  <si>
+    <t>Иконка {n}</t>
+  </si>
+  <si>
+    <t>cases.cover.icons</t>
+  </si>
+  <si>
+    <t>Icons</t>
+  </si>
+  <si>
+    <t>Иконки</t>
+  </si>
+  <si>
+    <t>cases.cover.option</t>
+  </si>
+  <si>
+    <t>Cover {n}</t>
+  </si>
+  <si>
+    <t>Обложка {n}</t>
+  </si>
+  <si>
+    <t>cases.cover.subtitle</t>
+  </si>
+  <si>
+    <t>Attorneys see this picture instead of your photo. Your photos stay hidden until you accept a bid.</t>
+  </si>
+  <si>
+    <t>Адвокаты видят эту картинку вместо вашего фото. Ваши фото скрыты, пока вы не примете ставку.</t>
+  </si>
+  <si>
+    <t>cases.cover.title</t>
+  </si>
+  <si>
+    <t>Card cover</t>
+  </si>
+  <si>
+    <t>Обложка карточки</t>
+  </si>
+  <si>
+    <t>cases.create.urgency.title</t>
+  </si>
+  <si>
+    <t>How soon do you need an attorney?</t>
+  </si>
+  <si>
+    <t>Как скоро нужен адвокат?</t>
+  </si>
+  <si>
+    <t>cases.facts.budget</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Бюджет</t>
+  </si>
+  <si>
+    <t>cases.facts.negotiable</t>
+  </si>
+  <si>
+    <t>Negotiable</t>
+  </si>
+  <si>
+    <t>Обсуждается</t>
+  </si>
+  <si>
+    <t>cases.facts.notSet</t>
+  </si>
+  <si>
+    <t>Not set</t>
+  </si>
+  <si>
+    <t>Не указано</t>
+  </si>
+  <si>
+    <t>cases.facts.state</t>
+  </si>
+  <si>
+    <t>cases.facts.urgency</t>
+  </si>
+  <si>
+    <t>Urgency</t>
+  </si>
+  <si>
+    <t>Срочность</t>
+  </si>
+  <si>
+    <t>cases.field.urgency</t>
+  </si>
+  <si>
+    <t>cases.mine.archived</t>
+  </si>
+  <si>
+    <t>Archive</t>
+  </si>
+  <si>
+    <t>Архив</t>
+  </si>
+  <si>
+    <t>cases.mine.finished</t>
+  </si>
+  <si>
+    <t>Finished</t>
+  </si>
+  <si>
+    <t>Закрытые</t>
+  </si>
+  <si>
+    <t>cases.outsideStates.attorney</t>
+  </si>
+  <si>
+    <t>You have no license in this case's state. You can still bid: the client will see the states you're licensed in.</t>
+  </si>
+  <si>
+    <t>У вас нет лицензии в штате этого кейса. Отклик отправить можно: клиент увидит, в каких штатах вы лицензированы.</t>
+  </si>
+  <si>
+    <t>cases.outsideStates.client</t>
+  </si>
+  <si>
+    <t>The attorney is licensed in: {states}. This case's state isn't one of them. Ask how they'll handle it.</t>
+  </si>
+  <si>
+    <t>Адвокат лицензирован в: {states}. Штата этого кейса среди них нет. Уточните, как будет вестись дело.</t>
+  </si>
+  <si>
+    <t>cases.outsideStates.clientNoList</t>
+  </si>
+  <si>
+    <t>The attorney has no license in this case's state. Ask how they'll handle it.</t>
+  </si>
+  <si>
+    <t>У адвоката нет лицензии в штате этого кейса. Уточните, как будет вестись дело.</t>
+  </si>
+  <si>
+    <t>cases.overview.meta</t>
+  </si>
+  <si>
+    <t>Published {published} · Accepted {accepted} · {bids} bids</t>
+  </si>
+  <si>
+    <t>Опубликован {published} · Принят {accepted} · Бидов: {bids}</t>
+  </si>
+  <si>
+    <t>cases.owner.closeShort</t>
+  </si>
+  <si>
+    <t>cases.owner.keepAliveShort</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>cases.owner.keptAlive</t>
+  </si>
+  <si>
+    <t>Your case stays open</t>
+  </si>
+  <si>
+    <t>Кейс остаётся открытым</t>
+  </si>
+  <si>
+    <t>cases.owner.staleShort</t>
+  </si>
+  <si>
+    <t>Still relevant?</t>
+  </si>
+  <si>
+    <t>Кейс ещё актуален?</t>
+  </si>
+  <si>
+    <t>cases.photos.failedHint</t>
+  </si>
+  <si>
+    <t>Retry or remove the file that failed to upload.</t>
+  </si>
+  <si>
+    <t>Повторите или удалите файл, который не загрузился.</t>
+  </si>
+  <si>
+    <t>cases.urgency.flexible</t>
+  </si>
+  <si>
+    <t>No rush</t>
+  </si>
+  <si>
+    <t>Не срочно</t>
+  </si>
+  <si>
+    <t>cases.urgency.soon</t>
+  </si>
+  <si>
+    <t>This week</t>
+  </si>
+  <si>
+    <t>На этой неделе</t>
+  </si>
+  <si>
+    <t>cases.urgency.urgent</t>
+  </si>
+  <si>
+    <t>Urgent</t>
+  </si>
+  <si>
+    <t>Срочно</t>
+  </si>
+  <si>
+    <t>invite.mismatch.practice</t>
+  </si>
+  <si>
+    <t>This case is outside the attorney's practice areas.</t>
+  </si>
+  <si>
+    <t>Дело не в практиках этого адвоката.</t>
+  </si>
+  <si>
+    <t>invite.mismatch.state</t>
+  </si>
+  <si>
+    <t>This attorney has no licence in the case's state.</t>
+  </si>
+  <si>
+    <t>У адвоката нет лицензии в штате этого дела.</t>
+  </si>
+  <si>
+    <t>invite.offer.alreadyBid</t>
+  </si>
+  <si>
+    <t>This attorney already sent a bid on this case.</t>
+  </si>
+  <si>
+    <t>Этот адвокат уже прислал бид на это дело.</t>
+  </si>
+  <si>
+    <t>invite.offer.body</t>
+  </si>
+  <si>
+    <t>The attorney sees the case and answers with a bid or declines. Your name and contacts stay hidden until you accept a bid.</t>
+  </si>
+  <si>
+    <t>Адвокат увидит дело и ответит бидом или откажется. Ваше имя и контакты скрыты, пока вы не примете бид.</t>
+  </si>
+  <si>
+    <t>invite.offer.budgetHint</t>
+  </si>
+  <si>
+    <t>invite.offer.createCase</t>
+  </si>
+  <si>
+    <t>Create a case</t>
+  </si>
+  <si>
+    <t>Создать дело</t>
+  </si>
+  <si>
+    <t>invite.offer.message</t>
+  </si>
+  <si>
+    <t>Note to the attorney</t>
+  </si>
+  <si>
+    <t>Сообщение адвокату</t>
+  </si>
+  <si>
+    <t>invite.offer.messageHint</t>
+  </si>
+  <si>
+    <t>Optional. No phone numbers or emails.</t>
+  </si>
+  <si>
+    <t>Необязательно. Без телефонов и email.</t>
+  </si>
+  <si>
+    <t>invite.offer.noCases</t>
+  </si>
+  <si>
+    <t>You have no open cases. Create one, then offer it to the attorney.</t>
+  </si>
+  <si>
+    <t>У вас нет открытых дел. Создайте дело, а потом предложите его адвокату.</t>
+  </si>
+  <si>
+    <t>invite.offer.pickCase</t>
+  </si>
+  <si>
+    <t>Which case?</t>
+  </si>
+  <si>
+    <t>Какое дело?</t>
+  </si>
+  <si>
+    <t>invite.offer.send</t>
+  </si>
+  <si>
+    <t>invite.offer.sent</t>
+  </si>
+  <si>
+    <t>Sent. We'll let you know when the attorney answers.</t>
+  </si>
+  <si>
+    <t>Отправлено. Мы сообщим, когда адвокат ответит.</t>
+  </si>
+  <si>
+    <t>invite.offer.title</t>
+  </si>
+  <si>
+    <t>Offer a case to {name}</t>
+  </si>
+  <si>
+    <t>Предложить дело: {name}</t>
+  </si>
+  <si>
+    <t>invites.answer</t>
+  </si>
+  <si>
+    <t>Answer with a bid</t>
+  </si>
+  <si>
+    <t>Ответить бидом</t>
+  </si>
+  <si>
+    <t>invites.budget</t>
+  </si>
+  <si>
+    <t>Client's budget: {amount}</t>
+  </si>
+  <si>
+    <t>Бюджет клиента: {amount}</t>
+  </si>
+  <si>
+    <t>invites.clientNote</t>
+  </si>
+  <si>
+    <t>Client's note</t>
+  </si>
+  <si>
+    <t>Сообщение клиента</t>
+  </si>
+  <si>
+    <t>invites.decline</t>
+  </si>
+  <si>
+    <t>Decline</t>
+  </si>
+  <si>
+    <t>Отказаться</t>
+  </si>
+  <si>
+    <t>invites.decline.confirm</t>
+  </si>
+  <si>
+    <t>invites.decline.reason</t>
+  </si>
+  <si>
+    <t>Reason (optional, the client sees it)</t>
+  </si>
+  <si>
+    <t>Причина (необязательно, клиент её увидит)</t>
+  </si>
+  <si>
+    <t>invites.decline.title</t>
+  </si>
+  <si>
+    <t>Decline the case?</t>
+  </si>
+  <si>
+    <t>Отказаться от дела?</t>
+  </si>
+  <si>
+    <t>invites.declined</t>
+  </si>
+  <si>
+    <t>Declined. The client was told.</t>
+  </si>
+  <si>
+    <t>Вы отказались. Клиент получил уведомление.</t>
+  </si>
+  <si>
+    <t>invites.empty</t>
+  </si>
+  <si>
+    <t>No invitations yet</t>
+  </si>
+  <si>
+    <t>Пока нет приглашений</t>
+  </si>
+  <si>
+    <t>invites.empty.body</t>
+  </si>
+  <si>
+    <t>When a client offers you a case, it appears here.</t>
+  </si>
+  <si>
+    <t>Когда клиент предложит вам дело, оно появится здесь.</t>
+  </si>
+  <si>
+    <t>invites.expires</t>
+  </si>
+  <si>
+    <t>Answer by {date}</t>
+  </si>
+  <si>
+    <t>Ответить до {date}</t>
+  </si>
+  <si>
+    <t>invites.noBudget</t>
+  </si>
+  <si>
+    <t>Budget to discuss</t>
+  </si>
+  <si>
+    <t>Бюджет обсуждается</t>
+  </si>
+  <si>
+    <t>invites.open</t>
+  </si>
+  <si>
+    <t>Open case</t>
+  </si>
+  <si>
+    <t>Открыть дело</t>
+  </si>
+  <si>
+    <t>invites.section</t>
+  </si>
+  <si>
+    <t>Invitations</t>
+  </si>
+  <si>
+    <t>Приглашения</t>
+  </si>
+  <si>
+    <t>invites.title</t>
+  </si>
+  <si>
+    <t>Invitations from clients</t>
+  </si>
+  <si>
+    <t>Приглашения от клиентов</t>
+  </si>
+  <si>
+    <t>invite.offer.budget</t>
+  </si>
+  <si>
+    <t>Your budget, $</t>
+  </si>
+  <si>
+    <t>Ваш бюджет, $</t>
+  </si>
+  <si>
+    <t>cases.files.count.few</t>
+  </si>
+  <si>
+    <t>cases.files.count.many</t>
+  </si>
+  <si>
+    <t>{count} файлов</t>
   </si>
 </sst>
 </file>
@@ -6654,7 +7920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C751"/>
+  <dimension ref="A1:C904"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -14922,6 +16188,1689 @@
         <v>2088</v>
       </c>
     </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A752" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B752" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C752" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A753" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B753" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C753" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A754" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B754" t="s">
+        <v>90</v>
+      </c>
+      <c r="C754" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A755" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B755" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C755" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A756" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B756" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C756" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A757" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B757" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C757" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A758" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B758" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C758" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A759" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B759" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C759" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A760" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B760" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C760" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A761" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B761" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C761" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A762" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B762" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C762" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A763" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B763" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C763" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A764" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B764" t="s">
+        <v>970</v>
+      </c>
+      <c r="C764" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A765" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B765" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C765" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A766" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B766" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C766" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A767" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B767" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C767" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A768" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B768" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C768" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A769" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B769" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C769" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A770" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B770" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C770" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A771" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B771" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C771" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A772" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B772" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C772" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A773" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B773" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C773" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A774" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B774" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C774" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A775" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B775" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C775" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A776" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B776" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C776" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A777" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B777" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C777" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A778" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B778" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C778" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A779" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B779" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C779" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A780" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B780" t="s">
+        <v>270</v>
+      </c>
+      <c r="C780" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A781" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B781" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C781" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A782" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B782" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C782" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A783" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B783" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C783" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A784" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B784" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C784" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A785" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B785" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C785" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A786" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B786" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C786" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A787" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B787" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C787" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A788" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B788" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C788" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A789" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B789" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C789" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A790" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B790" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C790" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A791" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B791" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C791" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A792" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B792" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C792" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A793" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B793" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C793" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A794" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B794" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C794" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A795" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B795" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C795" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A796" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B796" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C796" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A797" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B797" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C797" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A798" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B798" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C798" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A799" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B799" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C799" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A800" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B800" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C800" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A801" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B801" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C801" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A802" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B802" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C802" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B803" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C803" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A804" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B804" t="s">
+        <v>220</v>
+      </c>
+      <c r="C804" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A805" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B805" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C805" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B806" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C806" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A807" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B807" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C807" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A808" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B808" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C808" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A809" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B809" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C809" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A810" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B810" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C810" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B811" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C811" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B812" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C812" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B813" t="s">
+        <v>356</v>
+      </c>
+      <c r="C813" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B814" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C814" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B815" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C815" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B816" t="s">
+        <v>344</v>
+      </c>
+      <c r="C816" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B817" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C817" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A818" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B818" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C818" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A819" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B819" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C819" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A820" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B820" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C820" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A821" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B821" t="s">
+        <v>100</v>
+      </c>
+      <c r="C821" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A822" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B822" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C822" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A823" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B823" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C823" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A824" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B824" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C824" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B825" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C825" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B826" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C826" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B827" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C827" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A828" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B828" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C828" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A829" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B829" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C829" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A830" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B830" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C830" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A831" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B831" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C831" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A832" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B832" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C832" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B833" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C833" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A834" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B834" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C834" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A835" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B835" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C835" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A836" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B836" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C836" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A837" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B837" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C837" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A838" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B838" t="s">
+        <v>95</v>
+      </c>
+      <c r="C838" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A839" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B839" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C839" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A840" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B840" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C840" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A841" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B841" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C841" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A842" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B842" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C842" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A843" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B843" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C843" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A844" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B844" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C844" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A845" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B845" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C845" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A846" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B846" t="s">
+        <v>2350</v>
+      </c>
+      <c r="C846" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A847" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B847" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C847" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A848" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B848" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C848" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B849" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C849" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A850" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B850" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C850" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A851" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B851" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C851" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B852" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C852" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B853" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C853" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B854" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C854" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B855" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C855" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B856" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C856" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C857" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A858" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B858" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C858" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A859" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B859" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C859" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A860" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B860" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C860" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A861" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B861" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C861" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A862" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B862" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C862" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A863" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B863" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C863" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A864" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B864" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C864" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A865" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B865" t="s">
+        <v>2403</v>
+      </c>
+      <c r="C865" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A866" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B866" t="s">
+        <v>344</v>
+      </c>
+      <c r="C866" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A867" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B867" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C867" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A868" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B868" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C868" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A869" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B869" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C869" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A870" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B870" t="s">
+        <v>2416</v>
+      </c>
+      <c r="C870" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A871" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B871" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C871" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A872" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B872" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C872" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A873" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B873" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C873" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A874" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B874" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C874" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A875" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B875" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C875" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A876" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B876" t="s">
+        <v>2434</v>
+      </c>
+      <c r="C876" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A877" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B877" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C877" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A878" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B878" t="s">
+        <v>359</v>
+      </c>
+      <c r="C878" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A879" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B879" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C879" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A880" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B880" t="s">
+        <v>2444</v>
+      </c>
+      <c r="C880" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A881" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B881" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C881" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A882" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B882" t="s">
+        <v>2450</v>
+      </c>
+      <c r="C882" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A883" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B883" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C883" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A884" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B884" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C884" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A885" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B885" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C885" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A886" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B886" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C886" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A887" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B887" t="s">
+        <v>2463</v>
+      </c>
+      <c r="C887" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A888" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B888" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C888" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A889" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B889" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C889" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A890" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B890" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C890" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A891" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B891" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C891" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A892" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B892" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C892" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A893" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B893" t="s">
+        <v>2479</v>
+      </c>
+      <c r="C893" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A894" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B894" t="s">
+        <v>2482</v>
+      </c>
+      <c r="C894" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A895" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B895" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C895" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A896" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B896" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C896" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A897" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B897" t="s">
+        <v>2491</v>
+      </c>
+      <c r="C897" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A898" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B898" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C898" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A899" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B899" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C899" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A900" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B900" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C900" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A901" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B901" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C901" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A902" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B902" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C902" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A903" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B903" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C903" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A904" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B904" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C904" t="s">
+        <v>2510</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
